--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4C2B29-F795-9E45-B244-442455967A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D70E183-0643-014D-B05C-B42AEDC6D7CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -464,9 +464,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -474,10 +471,13 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -895,57 +895,57 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C4" s="11">
-        <v>51007</v>
+        <v>53997</v>
       </c>
       <c r="D4" s="11">
-        <v>54000</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="13"/>
+        <v>57000</v>
+      </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
+      <c r="H4" s="27" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C5" s="11">
-        <v>51002</v>
+        <v>51007</v>
       </c>
       <c r="D5" s="11">
         <v>54000</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="13"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C6" s="11">
-        <v>53997</v>
+        <v>51002</v>
       </c>
       <c r="D6" s="11">
-        <v>57000</v>
-      </c>
+        <v>54000</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="13"/>
       <c r="G6" s="26"/>
-      <c r="H6" s="27" t="s">
-        <v>50</v>
-      </c>
+      <c r="H6" s="26"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
@@ -960,8 +960,8 @@
       <c r="D7" s="11">
         <v>51000</v>
       </c>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24" t="s">
+      <c r="G7" s="22"/>
+      <c r="H7" s="23" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1216,13 +1216,13 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C22" s="10">
-        <v>28960</v>
+        <v>30040</v>
       </c>
       <c r="D22" s="10">
         <v>33000</v>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C23" s="10">
-        <v>27101</v>
+        <v>28960</v>
       </c>
       <c r="D23" s="10">
-        <v>30000</v>
+        <v>33000</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="13"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D70E183-0643-014D-B05C-B42AEDC6D7CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC07230B-2979-0442-B362-7F47164C6B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -403,7 +403,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -472,9 +472,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -907,7 +904,7 @@
         <v>57000</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="27" t="s">
+      <c r="H4" s="26" t="s">
         <v>50</v>
       </c>
     </row>
@@ -944,8 +941,8 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="13"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
@@ -987,87 +984,86 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C9" s="11">
-        <v>44912</v>
+        <v>44969</v>
       </c>
       <c r="D9" s="11">
         <v>48000</v>
       </c>
       <c r="E9" s="3"/>
-      <c r="F9" s="13" t="s">
-        <v>67</v>
-      </c>
+      <c r="F9" s="13"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C10" s="11">
-        <v>42145</v>
+        <v>44912</v>
       </c>
       <c r="D10" s="11">
-        <v>45000</v>
-      </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+        <v>48000</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="13" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C11" s="11">
-        <v>42037</v>
+        <v>42145</v>
       </c>
       <c r="D11" s="11">
         <v>45000</v>
       </c>
-      <c r="E11" s="3"/>
+      <c r="E11" s="8"/>
       <c r="F11" s="13"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11">
-        <v>41984</v>
+        <v>42037</v>
       </c>
       <c r="D12" s="11">
         <v>45000</v>
       </c>
-      <c r="E12" s="6"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="13"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="12">
-        <v>39096</v>
-      </c>
-      <c r="D13" s="12">
-        <v>42000</v>
+        <v>11</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="11">
+        <v>41984</v>
+      </c>
+      <c r="D13" s="11">
+        <v>45000</v>
       </c>
       <c r="E13" s="6"/>
       <c r="G13" s="4"/>
@@ -1075,55 +1071,56 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C14" s="12">
-        <v>38957</v>
+        <v>39096</v>
       </c>
       <c r="D14" s="12">
         <v>42000</v>
       </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="13"/>
+      <c r="E14" s="6"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>27</v>
-      </c>
       <c r="C15" s="12">
-        <v>38919</v>
+        <v>38957</v>
       </c>
       <c r="D15" s="12">
         <v>42000</v>
       </c>
       <c r="E15" s="3"/>
-      <c r="F15" s="13" t="s">
-        <v>63</v>
-      </c>
+      <c r="F15" s="13"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C16" s="12">
-        <v>36148</v>
+        <v>38919</v>
       </c>
       <c r="D16" s="12">
-        <v>39000</v>
+        <v>42000</v>
       </c>
       <c r="E16" s="3"/>
-      <c r="F16" s="13"/>
+      <c r="F16" s="13" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
@@ -1234,13 +1231,13 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C23" s="10">
-        <v>28960</v>
+        <v>29818</v>
       </c>
       <c r="D23" s="10">
         <v>33000</v>
@@ -1252,16 +1249,16 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C24" s="10">
-        <v>27087</v>
+        <v>28960</v>
       </c>
       <c r="D24" s="10">
-        <v>30000</v>
+        <v>33000</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="13"/>
@@ -1270,47 +1267,47 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="C25" s="10">
-        <v>26978</v>
+        <v>27087</v>
       </c>
       <c r="D25" s="10">
         <v>30000</v>
       </c>
+      <c r="E25" s="8"/>
+      <c r="F25" s="13"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="C26" s="10">
-        <v>26924</v>
+        <v>26978</v>
       </c>
       <c r="D26" s="10">
         <v>30000</v>
       </c>
-      <c r="E26" s="8"/>
-      <c r="F26" s="13"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C27" s="10">
-        <v>26855</v>
+        <v>26924</v>
       </c>
       <c r="D27" s="10">
         <v>30000</v>
@@ -1322,37 +1319,37 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C28" s="10">
-        <v>24116</v>
+        <v>26855</v>
       </c>
       <c r="D28" s="10">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="E28" s="8"/>
       <c r="F28" s="13"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C29" s="10">
-        <v>24067</v>
+        <v>24116</v>
       </c>
       <c r="D29" s="10">
         <v>27000</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="13"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="2">

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC07230B-2979-0442-B362-7F47164C6B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0532428B-ADD5-5547-99C2-A15A9272A335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1231,13 +1231,13 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C23" s="10">
-        <v>29818</v>
+        <v>29966</v>
       </c>
       <c r="D23" s="10">
         <v>33000</v>
@@ -1249,13 +1249,13 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C24" s="10">
-        <v>28960</v>
+        <v>29818</v>
       </c>
       <c r="D24" s="10">
         <v>33000</v>
@@ -1267,16 +1267,16 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C25" s="10">
-        <v>27087</v>
+        <v>28960</v>
       </c>
       <c r="D25" s="10">
-        <v>30000</v>
+        <v>33000</v>
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="13"/>
@@ -1285,47 +1285,47 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="C26" s="10">
-        <v>26978</v>
+        <v>27087</v>
       </c>
       <c r="D26" s="10">
         <v>30000</v>
       </c>
+      <c r="E26" s="8"/>
+      <c r="F26" s="13"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="C27" s="10">
-        <v>26924</v>
+        <v>26978</v>
       </c>
       <c r="D27" s="10">
         <v>30000</v>
       </c>
-      <c r="E27" s="8"/>
-      <c r="F27" s="13"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C28" s="10">
-        <v>26855</v>
+        <v>26924</v>
       </c>
       <c r="D28" s="10">
         <v>30000</v>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0532428B-ADD5-5547-99C2-A15A9272A335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7DB681-EEC6-684F-AB17-4EF2FEDDAF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1439,16 +1439,16 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C35" s="10">
-        <v>18092</v>
+        <v>21044</v>
       </c>
       <c r="D35" s="10">
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="13"/>
@@ -1457,49 +1457,49 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C36" s="10">
-        <v>18072</v>
+        <v>18092</v>
       </c>
       <c r="D36" s="10">
         <v>21000</v>
       </c>
-      <c r="E36" s="8"/>
+      <c r="E36" s="3"/>
       <c r="F36" s="13"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="C37" s="10">
-        <v>18055</v>
+        <v>18072</v>
       </c>
       <c r="D37" s="10">
         <v>21000</v>
       </c>
-      <c r="E37" s="3"/>
+      <c r="E37" s="8"/>
       <c r="F37" s="13"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C38" s="10">
-        <v>17994</v>
+        <v>18055</v>
       </c>
       <c r="D38" s="10">
         <v>21000</v>
@@ -1581,88 +1581,88 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C43" s="10">
-        <v>15036</v>
+        <v>15070</v>
       </c>
       <c r="D43" s="10">
         <v>18000</v>
       </c>
-      <c r="E43" s="3"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C44" s="10">
-        <v>14955</v>
+        <v>15036</v>
       </c>
       <c r="D44" s="10">
         <v>18000</v>
       </c>
-      <c r="E44" s="8"/>
-      <c r="F44" s="13"/>
+      <c r="E44" s="3"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C45" s="10">
-        <v>14692</v>
+        <v>14955</v>
       </c>
       <c r="D45" s="10">
         <v>18000</v>
       </c>
-      <c r="E45" s="3"/>
+      <c r="E45" s="8"/>
       <c r="F45" s="13"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="C46" s="10">
-        <v>12030</v>
+        <v>14692</v>
       </c>
       <c r="D46" s="10">
-        <v>15000</v>
-      </c>
-      <c r="E46" s="8"/>
+        <v>18000</v>
+      </c>
+      <c r="E46" s="3"/>
       <c r="F46" s="13"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
+        <v>45</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>54</v>
-      </c>
       <c r="C47" s="10">
-        <v>12015</v>
+        <v>12030</v>
       </c>
       <c r="D47" s="10">
         <v>15000</v>
       </c>
+      <c r="E47" s="8"/>
+      <c r="F47" s="13"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
     </row>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7DB681-EEC6-684F-AB17-4EF2FEDDAF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8266815-C487-3F4F-9FF3-E2738E7C61CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1018,49 +1018,48 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C11" s="11">
-        <v>42145</v>
+        <v>44849</v>
       </c>
       <c r="D11" s="11">
-        <v>45000</v>
-      </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="13"/>
+        <v>48000</v>
+      </c>
+      <c r="E11" s="6"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C12" s="11">
-        <v>42037</v>
+        <v>42145</v>
       </c>
       <c r="D12" s="11">
         <v>45000</v>
       </c>
-      <c r="E12" s="3"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="13"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C13" s="11">
-        <v>41984</v>
+        <v>42073</v>
       </c>
       <c r="D13" s="11">
         <v>45000</v>
@@ -1069,20 +1068,21 @@
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
-        <v>12</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="12">
-        <v>39096</v>
-      </c>
-      <c r="D14" s="12">
-        <v>42000</v>
-      </c>
-      <c r="E14" s="6"/>
+        <v>10</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="11">
+        <v>42037</v>
+      </c>
+      <c r="D14" s="11">
+        <v>45000</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="13"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
@@ -1122,55 +1122,55 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="10">
-        <v>33048</v>
-      </c>
-      <c r="D17" s="10">
-        <v>36000</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>66</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="12">
+        <v>36063</v>
+      </c>
+      <c r="D17" s="12">
+        <v>39000</v>
+      </c>
+      <c r="E17" s="8"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C18" s="10">
-        <v>33033</v>
+        <v>33048</v>
       </c>
       <c r="D18" s="10">
         <v>36000</v>
       </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
+      <c r="F18" s="13" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="C19" s="10">
-        <v>33007</v>
+        <v>33033</v>
       </c>
       <c r="D19" s="10">
         <v>36000</v>
       </c>
-      <c r="E19" s="8"/>
+      <c r="E19" s="3"/>
       <c r="F19" s="13"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -1439,13 +1439,13 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C35" s="10">
-        <v>21044</v>
+        <v>21103</v>
       </c>
       <c r="D35" s="10">
         <v>24000</v>
@@ -1457,16 +1457,16 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C36" s="10">
-        <v>18092</v>
+        <v>21044</v>
       </c>
       <c r="D36" s="10">
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="13"/>
@@ -1475,102 +1475,102 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C37" s="10">
-        <v>18072</v>
+        <v>18092</v>
       </c>
       <c r="D37" s="10">
         <v>21000</v>
       </c>
-      <c r="E37" s="8"/>
+      <c r="E37" s="3"/>
       <c r="F37" s="13"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="C38" s="10">
-        <v>18055</v>
+        <v>18072</v>
       </c>
       <c r="D38" s="10">
         <v>21000</v>
       </c>
-      <c r="E38" s="3"/>
+      <c r="E38" s="8"/>
       <c r="F38" s="13"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C39" s="10">
-        <v>17906</v>
+        <v>17984</v>
       </c>
       <c r="D39" s="10">
         <v>21000</v>
       </c>
       <c r="E39" s="3"/>
-      <c r="F39" s="13"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C40" s="10">
-        <v>17868</v>
+        <v>17906</v>
       </c>
       <c r="D40" s="10">
         <v>21000</v>
       </c>
-      <c r="E40" s="8"/>
+      <c r="E40" s="3"/>
       <c r="F40" s="13"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="C41" s="10">
-        <v>17822</v>
+        <v>17868</v>
       </c>
       <c r="D41" s="10">
         <v>21000</v>
       </c>
-      <c r="E41" s="3"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="13"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="C42" s="10">
-        <v>17786</v>
+        <v>17822</v>
       </c>
       <c r="D42" s="10">
         <v>21000</v>
@@ -1581,87 +1581,87 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C43" s="10">
-        <v>15070</v>
+        <v>17786</v>
       </c>
       <c r="D43" s="10">
-        <v>18000</v>
-      </c>
+        <v>21000</v>
+      </c>
+      <c r="E43" s="3"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C44" s="10">
-        <v>15036</v>
+        <v>15153</v>
       </c>
       <c r="D44" s="10">
         <v>18000</v>
       </c>
-      <c r="E44" s="3"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="13"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C45" s="10">
-        <v>14955</v>
+        <v>15070</v>
       </c>
       <c r="D45" s="10">
         <v>18000</v>
       </c>
-      <c r="E45" s="8"/>
-      <c r="F45" s="13"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C46" s="10">
-        <v>14692</v>
+        <v>14955</v>
       </c>
       <c r="D46" s="10">
         <v>18000</v>
       </c>
-      <c r="E46" s="3"/>
+      <c r="E46" s="8"/>
       <c r="F46" s="13"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="C47" s="10">
-        <v>12030</v>
+        <v>14692</v>
       </c>
       <c r="D47" s="10">
-        <v>15000</v>
-      </c>
-      <c r="E47" s="8"/>
+        <v>18000</v>
+      </c>
+      <c r="E47" s="3"/>
       <c r="F47" s="13"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8266815-C487-3F4F-9FF3-E2738E7C61CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A605BB-07B4-7B49-BAFC-FF2F74404955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1319,13 +1319,13 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="C28" s="10">
-        <v>26924</v>
+        <v>26948</v>
       </c>
       <c r="D28" s="10">
         <v>30000</v>
@@ -1337,19 +1337,21 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C29" s="10">
-        <v>24116</v>
+        <v>26924</v>
       </c>
       <c r="D29" s="10">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="13"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
@@ -1359,10 +1361,10 @@
         <v>33</v>
       </c>
       <c r="C30" s="10">
-        <v>24003</v>
+        <v>26817</v>
       </c>
       <c r="D30" s="10">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="E30" s="8"/>
       <c r="F30" s="13"/>
@@ -1371,21 +1373,19 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="C31" s="10">
-        <v>23955</v>
+        <v>24116</v>
       </c>
       <c r="D31" s="10">
         <v>27000</v>
       </c>
       <c r="E31" s="8"/>
       <c r="F31" s="13"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
@@ -1511,83 +1511,84 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="C39" s="10">
-        <v>17984</v>
+        <v>17993</v>
       </c>
       <c r="D39" s="10">
         <v>21000</v>
       </c>
-      <c r="E39" s="3"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="13"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C40" s="10">
-        <v>17906</v>
+        <v>17984</v>
       </c>
       <c r="D40" s="10">
         <v>21000</v>
       </c>
       <c r="E40" s="3"/>
-      <c r="F40" s="13"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C41" s="10">
-        <v>17868</v>
+        <v>17906</v>
       </c>
       <c r="D41" s="10">
         <v>21000</v>
       </c>
-      <c r="E41" s="8"/>
+      <c r="E41" s="3"/>
       <c r="F41" s="13"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="C42" s="10">
-        <v>17822</v>
+        <v>17868</v>
       </c>
       <c r="D42" s="10">
         <v>21000</v>
       </c>
-      <c r="E42" s="3"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="13"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="C43" s="10">
-        <v>17786</v>
+        <v>17822</v>
       </c>
       <c r="D43" s="10">
         <v>21000</v>
@@ -1598,53 +1599,52 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C44" s="10">
-        <v>15153</v>
+        <v>17786</v>
       </c>
       <c r="D44" s="10">
-        <v>18000</v>
-      </c>
-      <c r="E44" s="8"/>
-      <c r="F44" s="13"/>
+        <v>21000</v>
+      </c>
+      <c r="E44" s="3"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
+        <v>45</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>54</v>
-      </c>
       <c r="C45" s="10">
-        <v>15070</v>
+        <v>15153</v>
       </c>
       <c r="D45" s="10">
         <v>18000</v>
       </c>
+      <c r="E45" s="8"/>
+      <c r="F45" s="13"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C46" s="10">
-        <v>14955</v>
+        <v>15070</v>
       </c>
       <c r="D46" s="10">
         <v>18000</v>
       </c>
-      <c r="E46" s="8"/>
-      <c r="F46" s="13"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
     </row>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A605BB-07B4-7B49-BAFC-FF2F74404955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993150FA-CFB2-EB4D-8355-79751A1E100C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1041,10 +1041,10 @@
         <v>32</v>
       </c>
       <c r="C12" s="11">
-        <v>42145</v>
+        <v>44806</v>
       </c>
       <c r="D12" s="11">
-        <v>45000</v>
+        <v>48000</v>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="13"/>
@@ -1439,31 +1439,31 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="C35" s="10">
-        <v>21103</v>
+        <v>21242</v>
       </c>
       <c r="D35" s="10">
         <v>24000</v>
       </c>
-      <c r="E35" s="3"/>
+      <c r="E35" s="8"/>
       <c r="F35" s="13"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C36" s="10">
-        <v>21044</v>
+        <v>21103</v>
       </c>
       <c r="D36" s="10">
         <v>24000</v>
@@ -1475,16 +1475,16 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C37" s="10">
-        <v>18092</v>
+        <v>21044</v>
       </c>
       <c r="D37" s="10">
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="13"/>
@@ -1493,18 +1493,18 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C38" s="10">
-        <v>18072</v>
+        <v>18092</v>
       </c>
       <c r="D38" s="10">
         <v>21000</v>
       </c>
-      <c r="E38" s="8"/>
+      <c r="E38" s="3"/>
       <c r="F38" s="13"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993150FA-CFB2-EB4D-8355-79751A1E100C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79DB54D-8C97-6042-B6D2-EACFDB5C0953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1493,119 +1493,119 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C38" s="10">
-        <v>18092</v>
+        <v>20854</v>
       </c>
       <c r="D38" s="10">
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="E38" s="3"/>
-      <c r="F38" s="13"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="C39" s="10">
-        <v>17993</v>
+        <v>18092</v>
       </c>
       <c r="D39" s="10">
         <v>21000</v>
       </c>
-      <c r="E39" s="8"/>
+      <c r="E39" s="3"/>
       <c r="F39" s="13"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="C40" s="10">
-        <v>17984</v>
+        <v>17993</v>
       </c>
       <c r="D40" s="10">
         <v>21000</v>
       </c>
-      <c r="E40" s="3"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="13"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C41" s="10">
-        <v>17906</v>
+        <v>17984</v>
       </c>
       <c r="D41" s="10">
         <v>21000</v>
       </c>
       <c r="E41" s="3"/>
-      <c r="F41" s="13"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C42" s="10">
-        <v>17868</v>
+        <v>17906</v>
       </c>
       <c r="D42" s="10">
         <v>21000</v>
       </c>
-      <c r="E42" s="8"/>
+      <c r="E42" s="3"/>
       <c r="F42" s="13"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="C43" s="10">
-        <v>17822</v>
+        <v>17868</v>
       </c>
       <c r="D43" s="10">
         <v>21000</v>
       </c>
-      <c r="E43" s="3"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="13"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="C44" s="10">
-        <v>17786</v>
+        <v>17822</v>
       </c>
       <c r="D44" s="10">
         <v>21000</v>
@@ -1668,34 +1668,32 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C48" s="10">
-        <v>11897</v>
+        <v>12074</v>
       </c>
       <c r="D48" s="10">
         <v>15000</v>
       </c>
-      <c r="E48" s="8"/>
-      <c r="F48" s="13"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C49" s="10">
-        <v>8977</v>
+        <v>11897</v>
       </c>
       <c r="D49" s="10">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="E49" s="8"/>
       <c r="F49" s="13"/>
@@ -1704,17 +1702,19 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C50" s="10">
-        <v>8847</v>
+        <v>8977</v>
       </c>
       <c r="D50" s="10">
         <v>12000</v>
       </c>
+      <c r="E50" s="8"/>
+      <c r="F50" s="13"/>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
     </row>
@@ -1726,10 +1726,10 @@
         <v>60</v>
       </c>
       <c r="C51" s="10">
-        <v>6044</v>
+        <v>8944</v>
       </c>
       <c r="D51" s="10">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79DB54D-8C97-6042-B6D2-EACFDB5C0953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793FD833-B299-0D4C-A220-9F8F5C4F04FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -403,7 +403,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -464,19 +464,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -903,64 +900,64 @@
       <c r="D4" s="11">
         <v>57000</v>
       </c>
-      <c r="G4" s="25"/>
-      <c r="H4" s="26" t="s">
+      <c r="G4" s="22"/>
+      <c r="H4" s="23" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C5" s="11">
-        <v>51007</v>
+        <v>51012</v>
       </c>
       <c r="D5" s="11">
         <v>54000</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="13"/>
       <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
+      <c r="H5" s="18" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C6" s="11">
-        <v>51002</v>
+        <v>51007</v>
       </c>
       <c r="D6" s="11">
         <v>54000</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="13"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C7" s="11">
-        <v>47939</v>
+        <v>51002</v>
       </c>
       <c r="D7" s="11">
-        <v>51000</v>
-      </c>
-      <c r="G7" s="22"/>
-      <c r="H7" s="23" t="s">
-        <v>9</v>
-      </c>
+        <v>54000</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2">

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793FD833-B299-0D4C-A220-9F8F5C4F04FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80458033-D0D2-0E46-AE34-4759D8C8BD13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
   <si>
     <t>No.</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>Accident repairs with a substandard touch</t>
+  </si>
+  <si>
+    <t>Needs Eng. Hanger rubber bush (11102-M9Q-3000)  X2 &amp; Eng Hanger 50351-ARA-0103</t>
   </si>
 </sst>
 </file>
@@ -403,7 +406,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -473,7 +476,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -880,7 +882,7 @@
       </c>
       <c r="E3" s="3"/>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G3" s="19"/>
       <c r="H3" s="20" t="s">
@@ -938,8 +940,6 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="13"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
@@ -1246,13 +1246,13 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C24" s="10">
-        <v>29818</v>
+        <v>29848</v>
       </c>
       <c r="D24" s="10">
         <v>33000</v>
@@ -1264,13 +1264,13 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C25" s="10">
-        <v>28960</v>
+        <v>29818</v>
       </c>
       <c r="D25" s="10">
         <v>33000</v>
@@ -1282,16 +1282,16 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C26" s="10">
-        <v>27087</v>
+        <v>28960</v>
       </c>
       <c r="D26" s="10">
-        <v>30000</v>
+        <v>33000</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="13"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80458033-D0D2-0E46-AE34-4759D8C8BD13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559F81EC-8EF6-3E4C-A049-2770FDAD7BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -967,10 +967,10 @@
         <v>24</v>
       </c>
       <c r="C8" s="11">
-        <v>47838</v>
+        <v>50855</v>
       </c>
       <c r="D8" s="11">
-        <v>51000</v>
+        <v>54000</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="13" t="s">
@@ -1083,18 +1083,18 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>13</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="12">
-        <v>38957</v>
-      </c>
-      <c r="D15" s="12">
-        <v>42000</v>
+      <c r="C15" s="11">
+        <v>41964</v>
+      </c>
+      <c r="D15" s="11">
+        <v>45000</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="13"/>
@@ -1386,13 +1386,13 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="C32" s="10">
-        <v>23891</v>
+        <v>24030</v>
       </c>
       <c r="D32" s="10">
         <v>27000</v>
@@ -1404,29 +1404,31 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C33" s="10">
-        <v>23812</v>
+        <v>23891</v>
       </c>
       <c r="D33" s="10">
         <v>27000</v>
       </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="13"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C34" s="10">
-        <v>23750</v>
+        <v>23812</v>
       </c>
       <c r="D34" s="10">
         <v>27000</v>
@@ -1436,49 +1438,47 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C35" s="10">
-        <v>21242</v>
+        <v>23750</v>
       </c>
       <c r="D35" s="10">
-        <v>24000</v>
-      </c>
-      <c r="E35" s="8"/>
-      <c r="F35" s="13"/>
+        <v>27000</v>
+      </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="C36" s="10">
-        <v>21103</v>
+        <v>21242</v>
       </c>
       <c r="D36" s="10">
         <v>24000</v>
       </c>
-      <c r="E36" s="3"/>
+      <c r="E36" s="8"/>
       <c r="F36" s="13"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C37" s="10">
-        <v>21044</v>
+        <v>21103</v>
       </c>
       <c r="D37" s="10">
         <v>24000</v>
@@ -1490,106 +1490,106 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C38" s="10">
-        <v>20854</v>
+        <v>21044</v>
       </c>
       <c r="D38" s="10">
         <v>24000</v>
       </c>
       <c r="E38" s="3"/>
+      <c r="F38" s="13"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C39" s="10">
-        <v>18092</v>
+        <v>20932</v>
       </c>
       <c r="D39" s="10">
-        <v>21000</v>
-      </c>
-      <c r="E39" s="3"/>
+        <v>24000</v>
+      </c>
+      <c r="E39" s="8"/>
       <c r="F39" s="13"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C40" s="10">
-        <v>17993</v>
+        <v>20854</v>
       </c>
       <c r="D40" s="10">
-        <v>21000</v>
-      </c>
-      <c r="E40" s="8"/>
-      <c r="F40" s="13"/>
+        <v>24000</v>
+      </c>
+      <c r="E40" s="3"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="C41" s="10">
-        <v>17984</v>
+        <v>17993</v>
       </c>
       <c r="D41" s="10">
         <v>21000</v>
       </c>
-      <c r="E41" s="3"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="13"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C42" s="10">
-        <v>17906</v>
+        <v>17984</v>
       </c>
       <c r="D42" s="10">
         <v>21000</v>
       </c>
       <c r="E42" s="3"/>
-      <c r="F42" s="13"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C43" s="10">
-        <v>17868</v>
+        <v>17906</v>
       </c>
       <c r="D43" s="10">
         <v>21000</v>
       </c>
-      <c r="E43" s="8"/>
+      <c r="E43" s="3"/>
       <c r="F43" s="13"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559F81EC-8EF6-3E4C-A049-2770FDAD7BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2834A6-7B22-A647-B804-AC5E5D9A6DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1288,10 +1288,10 @@
         <v>35</v>
       </c>
       <c r="C26" s="10">
-        <v>28960</v>
+        <v>33240</v>
       </c>
       <c r="D26" s="10">
-        <v>33000</v>
+        <v>36000</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="13"/>
@@ -1376,10 +1376,10 @@
         <v>47</v>
       </c>
       <c r="C31" s="10">
-        <v>24116</v>
+        <v>27114</v>
       </c>
       <c r="D31" s="10">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="E31" s="8"/>
       <c r="F31" s="13"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2834A6-7B22-A647-B804-AC5E5D9A6DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F92B160-0622-4B4F-B3B9-F74BB0C79AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="77">
   <si>
     <t>No.</t>
   </si>
@@ -241,7 +241,31 @@
     <t>Accident repairs with a substandard touch</t>
   </si>
   <si>
-    <t>Needs Eng. Hanger rubber bush (11102-M9Q-3000)  X2 &amp; Eng Hanger 50351-ARA-0103</t>
+    <t>ND17SHGP</t>
+  </si>
+  <si>
+    <t>ND17PTGP</t>
+  </si>
+  <si>
+    <t>ND17TKGP</t>
+  </si>
+  <si>
+    <t>ND17NPGP</t>
+  </si>
+  <si>
+    <t>ND17TZGP</t>
+  </si>
+  <si>
+    <t>ND17WHGP</t>
+  </si>
+  <si>
+    <t>ND17VPGP</t>
+  </si>
+  <si>
+    <t>ND17RKGP</t>
+  </si>
+  <si>
+    <t>ND17NFGP</t>
   </si>
 </sst>
 </file>
@@ -406,7 +430,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -439,9 +463,6 @@
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -475,6 +496,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -811,7 +838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD8F41E-515C-324C-BF16-60C17361A01E}">
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="27" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
@@ -839,141 +866,142 @@
         <v>3</v>
       </c>
       <c r="E1" s="3"/>
-      <c r="F1" s="13"/>
+      <c r="F1" s="12"/>
       <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="21"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C2" s="11">
-        <v>60031</v>
+        <v>44969</v>
       </c>
       <c r="D2" s="11">
-        <v>63000</v>
+        <v>48000</v>
       </c>
       <c r="E2" s="3"/>
-      <c r="F2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G2" s="17"/>
-      <c r="H2" s="18" t="s">
-        <v>6</v>
-      </c>
+      <c r="F2" s="12"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C3" s="11">
-        <v>56725</v>
+        <v>44912</v>
       </c>
       <c r="D3" s="11">
-        <v>60000</v>
+        <v>48000</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="19"/>
-      <c r="H3" s="20" t="s">
-        <v>64</v>
+      <c r="F3" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G3" s="16"/>
+      <c r="H3" s="17" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C4" s="11">
-        <v>53997</v>
+        <v>44806</v>
       </c>
       <c r="D4" s="11">
-        <v>57000</v>
-      </c>
-      <c r="G4" s="22"/>
-      <c r="H4" s="23" t="s">
-        <v>50</v>
+        <v>48000</v>
+      </c>
+      <c r="E4" s="8"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="19" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C5" s="11">
-        <v>51012</v>
+        <v>42073</v>
       </c>
       <c r="D5" s="11">
-        <v>54000</v>
-      </c>
-      <c r="G5" s="24"/>
-      <c r="H5" s="18" t="s">
-        <v>9</v>
+        <v>45000</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="22" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C6" s="11">
-        <v>51007</v>
+        <v>42037</v>
       </c>
       <c r="D6" s="11">
-        <v>54000</v>
+        <v>45000</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="13"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="17" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C7" s="11">
-        <v>51002</v>
+        <v>41964</v>
       </c>
       <c r="D7" s="11">
-        <v>54000</v>
+        <v>45000</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="F7" s="12"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="11">
-        <v>50855</v>
-      </c>
-      <c r="D8" s="11">
-        <v>54000</v>
+      <c r="B8" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="25">
+        <v>38919</v>
+      </c>
+      <c r="D8" s="25">
+        <v>42000</v>
       </c>
       <c r="E8" s="3"/>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="12" t="s">
         <v>63</v>
       </c>
       <c r="G8" s="4"/>
@@ -981,70 +1009,70 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
-        <v>14</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="11">
-        <v>44969</v>
-      </c>
-      <c r="D9" s="11">
-        <v>48000</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="13"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="25">
+        <v>36063</v>
+      </c>
+      <c r="D9" s="25">
+        <v>39000</v>
+      </c>
+      <c r="E9" s="8"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
-        <v>8</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="11">
-        <v>44912</v>
-      </c>
-      <c r="D10" s="11">
-        <v>48000</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="13" t="s">
-        <v>67</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="25">
+        <v>35951</v>
+      </c>
+      <c r="D10" s="25">
+        <v>39000</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" s="12"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
-        <v>11</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="11">
-        <v>44849</v>
-      </c>
-      <c r="D11" s="11">
-        <v>48000</v>
-      </c>
-      <c r="E11" s="6"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="10">
+        <v>33240</v>
+      </c>
+      <c r="D11" s="10">
+        <v>36000</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="11">
-        <v>44806</v>
-      </c>
-      <c r="D12" s="11">
-        <v>48000</v>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="13"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="10">
+        <v>33048</v>
+      </c>
+      <c r="D12" s="10">
+        <v>36000</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="12"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
@@ -1052,141 +1080,137 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="11">
-        <v>42073</v>
-      </c>
-      <c r="D13" s="11">
-        <v>45000</v>
-      </c>
-      <c r="E13" s="6"/>
+      <c r="B13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="10">
+        <v>32962</v>
+      </c>
+      <c r="D13" s="10">
+        <v>36000</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="12"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
-        <v>10</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="11">
-        <v>42037</v>
-      </c>
-      <c r="D14" s="11">
-        <v>45000</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="13"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="10">
+        <v>30071</v>
+      </c>
+      <c r="D14" s="10">
+        <v>33000</v>
+      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="12"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
-        <v>13</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="11">
-        <v>41964</v>
-      </c>
-      <c r="D15" s="11">
-        <v>45000</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="13"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="10">
+        <v>30040</v>
+      </c>
+      <c r="D15" s="10">
+        <v>33000</v>
+      </c>
+      <c r="E15" s="8"/>
+      <c r="F15" s="12"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="12">
-        <v>38919</v>
-      </c>
-      <c r="D16" s="12">
-        <v>42000</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="10">
+        <v>29966</v>
+      </c>
+      <c r="D16" s="10">
+        <v>33000</v>
+      </c>
+      <c r="E16" s="8"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
-        <v>18</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="12">
-        <v>36063</v>
-      </c>
-      <c r="D17" s="12">
-        <v>39000</v>
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="10">
+        <v>29848</v>
+      </c>
+      <c r="D17" s="10">
+        <v>33000</v>
       </c>
       <c r="E17" s="8"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="F17" s="12"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C18" s="10">
-        <v>33048</v>
+        <v>29818</v>
       </c>
       <c r="D18" s="10">
-        <v>36000</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>66</v>
-      </c>
+        <v>33000</v>
+      </c>
+      <c r="E18" s="8"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="C19" s="10">
-        <v>33033</v>
+        <v>27114</v>
       </c>
       <c r="D19" s="10">
-        <v>36000</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
+        <v>30000</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C20" s="10">
-        <v>32962</v>
+        <v>26978</v>
       </c>
       <c r="D20" s="10">
-        <v>36000</v>
+        <v>30000</v>
       </c>
       <c r="E20" s="8"/>
-      <c r="F20" s="13"/>
+      <c r="F20" s="12"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
@@ -1195,52 +1219,52 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C21" s="10">
-        <v>30071</v>
+        <v>26948</v>
       </c>
       <c r="D21" s="10">
-        <v>33000</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="13"/>
+        <v>30000</v>
+      </c>
+      <c r="E21" s="8"/>
+      <c r="F21" s="12"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C22" s="10">
-        <v>30040</v>
+        <v>26924</v>
       </c>
       <c r="D22" s="10">
-        <v>33000</v>
+        <v>30000</v>
       </c>
       <c r="E22" s="8"/>
-      <c r="F22" s="13"/>
+      <c r="F22" s="12"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C23" s="10">
-        <v>29966</v>
+        <v>26817</v>
       </c>
       <c r="D23" s="10">
-        <v>33000</v>
+        <v>30000</v>
       </c>
       <c r="E23" s="8"/>
-      <c r="F23" s="13"/>
+      <c r="F23" s="12"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
@@ -1249,104 +1273,102 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="C24" s="10">
-        <v>29848</v>
+        <v>24030</v>
       </c>
       <c r="D24" s="10">
-        <v>33000</v>
-      </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="13"/>
+        <v>27000</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="12"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C25" s="10">
-        <v>29818</v>
+        <v>23891</v>
       </c>
       <c r="D25" s="10">
-        <v>33000</v>
-      </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="13"/>
+        <v>27000</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="12"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="C26" s="10">
-        <v>33240</v>
+        <v>23812</v>
       </c>
       <c r="D26" s="10">
-        <v>36000</v>
-      </c>
-      <c r="E26" s="8"/>
-      <c r="F26" s="13"/>
+        <v>27000</v>
+      </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C27" s="10">
-        <v>26978</v>
+        <v>23750</v>
       </c>
       <c r="D27" s="10">
-        <v>30000</v>
+        <v>27000</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="C28" s="10">
-        <v>26948</v>
+        <v>21242</v>
       </c>
       <c r="D28" s="10">
-        <v>30000</v>
+        <v>24000</v>
       </c>
       <c r="E28" s="8"/>
-      <c r="F28" s="13"/>
+      <c r="F28" s="12"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="C29" s="10">
-        <v>26924</v>
+        <v>21103</v>
       </c>
       <c r="D29" s="10">
-        <v>30000</v>
-      </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="13"/>
+        <v>24000</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="12"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
     </row>
@@ -1355,100 +1377,102 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C30" s="10">
-        <v>26817</v>
+        <v>21044</v>
       </c>
       <c r="D30" s="10">
-        <v>30000</v>
-      </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="13"/>
+        <v>24000</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="12"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C31" s="10">
-        <v>27114</v>
+        <v>20932</v>
       </c>
       <c r="D31" s="10">
-        <v>30000</v>
+        <v>24000</v>
       </c>
       <c r="E31" s="8"/>
-      <c r="F31" s="13"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C32" s="10">
-        <v>24030</v>
+        <v>20854</v>
       </c>
       <c r="D32" s="10">
-        <v>27000</v>
+        <v>24000</v>
       </c>
       <c r="E32" s="3"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="C33" s="10">
-        <v>23891</v>
+        <v>17993</v>
       </c>
       <c r="D33" s="10">
-        <v>27000</v>
-      </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="13"/>
+        <v>21000</v>
+      </c>
+      <c r="E33" s="8"/>
+      <c r="F33" s="12"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="C34" s="10">
-        <v>23812</v>
+        <v>17984</v>
       </c>
       <c r="D34" s="10">
-        <v>27000</v>
-      </c>
+        <v>21000</v>
+      </c>
+      <c r="E34" s="3"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C35" s="10">
-        <v>23750</v>
+        <v>17906</v>
       </c>
       <c r="D35" s="10">
-        <v>27000</v>
-      </c>
+        <v>21000</v>
+      </c>
+      <c r="E35" s="3"/>
+      <c r="F35" s="12"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
     </row>
@@ -1457,16 +1481,15 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="C36" s="10">
-        <v>21242</v>
+        <v>17822</v>
       </c>
       <c r="D36" s="10">
-        <v>24000</v>
-      </c>
-      <c r="E36" s="8"/>
-      <c r="F36" s="13"/>
+        <v>21000</v>
+      </c>
+      <c r="E36" s="3"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
     </row>
@@ -1475,16 +1498,16 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="C37" s="10">
-        <v>21103</v>
+        <v>15153</v>
       </c>
       <c r="D37" s="10">
-        <v>24000</v>
-      </c>
-      <c r="E37" s="3"/>
-      <c r="F37" s="13"/>
+        <v>18000</v>
+      </c>
+      <c r="E37" s="8"/>
+      <c r="F37" s="12"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
@@ -1493,69 +1516,66 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C38" s="10">
-        <v>21044</v>
+        <v>15070</v>
       </c>
       <c r="D38" s="10">
-        <v>24000</v>
-      </c>
-      <c r="E38" s="3"/>
-      <c r="F38" s="13"/>
+        <v>18000</v>
+      </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="C39" s="10">
-        <v>20932</v>
+        <v>14692</v>
       </c>
       <c r="D39" s="10">
-        <v>24000</v>
-      </c>
-      <c r="E39" s="8"/>
-      <c r="F39" s="13"/>
+        <v>18000</v>
+      </c>
+      <c r="E39" s="3"/>
+      <c r="F39" s="12"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C40" s="10">
-        <v>20854</v>
+        <v>12074</v>
       </c>
       <c r="D40" s="10">
-        <v>24000</v>
-      </c>
-      <c r="E40" s="3"/>
+        <v>15000</v>
+      </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C41" s="10">
-        <v>17993</v>
+        <v>11897</v>
       </c>
       <c r="D41" s="10">
-        <v>21000</v>
+        <v>15000</v>
       </c>
       <c r="E41" s="8"/>
-      <c r="F41" s="13"/>
+      <c r="F41" s="12"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
@@ -1564,154 +1584,144 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="C42" s="10">
-        <v>17984</v>
+        <v>8977</v>
       </c>
       <c r="D42" s="10">
-        <v>21000</v>
-      </c>
-      <c r="E42" s="3"/>
+        <v>12000</v>
+      </c>
+      <c r="E42" s="8"/>
+      <c r="F42" s="12"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="C43" s="10">
-        <v>17906</v>
+        <v>8944</v>
       </c>
       <c r="D43" s="10">
-        <v>21000</v>
-      </c>
-      <c r="E43" s="3"/>
-      <c r="F43" s="13"/>
+        <v>12000</v>
+      </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="C44" s="10">
-        <v>17822</v>
+        <v>5970</v>
       </c>
       <c r="D44" s="10">
-        <v>21000</v>
-      </c>
-      <c r="E44" s="3"/>
+        <v>9000</v>
+      </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C45" s="10">
-        <v>15153</v>
+        <v>3008</v>
       </c>
       <c r="D45" s="10">
-        <v>18000</v>
-      </c>
-      <c r="E45" s="8"/>
-      <c r="F45" s="13"/>
+        <v>6000</v>
+      </c>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C46" s="10">
-        <v>15070</v>
+        <v>0</v>
       </c>
       <c r="D46" s="10">
-        <v>18000</v>
+        <v>1000</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="C47" s="10">
-        <v>14692</v>
+        <v>0</v>
       </c>
       <c r="D47" s="10">
-        <v>18000</v>
-      </c>
-      <c r="E47" s="3"/>
-      <c r="F47" s="13"/>
+        <v>1000</v>
+      </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C48" s="10">
-        <v>12074</v>
+        <v>0</v>
       </c>
       <c r="D48" s="10">
-        <v>15000</v>
+        <v>1000</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="C49" s="10">
-        <v>11897</v>
+        <v>0</v>
       </c>
       <c r="D49" s="10">
-        <v>15000</v>
-      </c>
-      <c r="E49" s="8"/>
-      <c r="F49" s="13"/>
+        <v>1000</v>
+      </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="C50" s="10">
-        <v>8977</v>
+        <v>0</v>
       </c>
       <c r="D50" s="10">
-        <v>12000</v>
-      </c>
-      <c r="E50" s="8"/>
-      <c r="F50" s="13"/>
+        <v>1000</v>
+      </c>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
     </row>
@@ -1720,13 +1730,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C51" s="10">
-        <v>8944</v>
+        <v>0</v>
       </c>
       <c r="D51" s="10">
-        <v>12000</v>
+        <v>1000</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -1736,13 +1746,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="C52" s="10">
-        <v>2967</v>
+        <v>0</v>
       </c>
       <c r="D52" s="10">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
@@ -1752,13 +1762,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C53" s="10">
-        <v>1060</v>
+        <v>0</v>
       </c>
       <c r="D53" s="10">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -1767,31 +1777,189 @@
       <c r="A54" s="2">
         <v>53</v>
       </c>
-      <c r="B54" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C54" s="16">
-        <v>982</v>
-      </c>
-      <c r="D54" s="16">
-        <v>3000</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F54" s="14" t="s">
-        <v>61</v>
+      <c r="B54" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C54" s="10">
+        <v>0</v>
+      </c>
+      <c r="D54" s="10">
+        <v>1000</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35"/>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35"/>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35"/>
-    <row r="65" x14ac:dyDescent="0.35"/>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A55" s="2">
+        <v>54</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55" s="15">
+        <v>60031</v>
+      </c>
+      <c r="D55" s="15">
+        <v>63000</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F55" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A56" s="2">
+        <v>55</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C56" s="15">
+        <v>56725</v>
+      </c>
+      <c r="D56" s="15">
+        <v>60000</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A57" s="2">
+        <v>56</v>
+      </c>
+      <c r="B57" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C57" s="15">
+        <v>53997</v>
+      </c>
+      <c r="D57" s="15">
+        <v>57000</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A58" s="2">
+        <v>57</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="15">
+        <v>51012</v>
+      </c>
+      <c r="D58" s="15">
+        <v>54000</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A59" s="2">
+        <v>58</v>
+      </c>
+      <c r="B59" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" s="15">
+        <v>51007</v>
+      </c>
+      <c r="D59" s="15">
+        <v>54000</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F59" s="12"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A60" s="2">
+        <v>59</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" s="15">
+        <v>51002</v>
+      </c>
+      <c r="D60" s="15">
+        <v>54000</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F60" s="12"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A61" s="2">
+        <v>60</v>
+      </c>
+      <c r="B61" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="15">
+        <v>50855</v>
+      </c>
+      <c r="D61" s="15">
+        <v>54000</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F61" s="12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" s="15">
+        <v>44849</v>
+      </c>
+      <c r="D62" s="15">
+        <v>48000</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F62" s="12"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A63" s="2">
+        <v>62</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C63" s="15">
+        <v>982</v>
+      </c>
+      <c r="D63" s="15">
+        <v>3000</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F63" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A64" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:H54">
-    <sortCondition descending="1" ref="C1:C54"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F54">
+    <sortCondition descending="1" ref="C2:C54"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F92B160-0622-4B4F-B3B9-F74BB0C79AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8292FBB9-6549-1047-BEEC-8DAC3E841875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C2" s="11">
-        <v>44969</v>
+        <v>45003</v>
       </c>
       <c r="D2" s="11">
         <v>48000</v>
@@ -895,18 +895,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C3" s="11">
-        <v>44912</v>
+        <v>44969</v>
       </c>
       <c r="D3" s="11">
         <v>48000</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="12" t="s">
-        <v>67</v>
-      </c>
+      <c r="F3" s="12"/>
       <c r="G3" s="16"/>
       <c r="H3" s="17" t="s">
         <v>6</v>
@@ -917,16 +915,18 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C4" s="11">
-        <v>44806</v>
+        <v>44912</v>
       </c>
       <c r="D4" s="11">
         <v>48000</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="12"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="12" t="s">
+        <v>67</v>
+      </c>
       <c r="G4" s="18"/>
       <c r="H4" s="19" t="s">
         <v>64</v>
@@ -937,15 +937,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C5" s="11">
-        <v>42073</v>
+        <v>44806</v>
       </c>
       <c r="D5" s="11">
-        <v>45000</v>
-      </c>
-      <c r="E5" s="6"/>
+        <v>48000</v>
+      </c>
+      <c r="E5" s="8"/>
+      <c r="F5" s="12"/>
       <c r="G5" s="21"/>
       <c r="H5" s="22" t="s">
         <v>50</v>
@@ -956,16 +957,15 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C6" s="11">
-        <v>42037</v>
+        <v>42073</v>
       </c>
       <c r="D6" s="11">
         <v>45000</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="12"/>
+      <c r="E6" s="6"/>
       <c r="G6" s="23"/>
       <c r="H6" s="17" t="s">
         <v>9</v>
@@ -991,14 +991,14 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="25">
-        <v>38919</v>
-      </c>
-      <c r="D8" s="25">
-        <v>42000</v>
+      <c r="C8" s="11">
+        <v>41702</v>
+      </c>
+      <c r="D8" s="11">
+        <v>45000</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="12" t="s">
@@ -1081,15 +1081,15 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C13" s="10">
-        <v>32962</v>
+        <v>33043</v>
       </c>
       <c r="D13" s="10">
         <v>36000</v>
       </c>
-      <c r="E13" s="3"/>
+      <c r="E13" s="8"/>
       <c r="F13" s="12"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
@@ -1099,13 +1099,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C14" s="10">
-        <v>30071</v>
+        <v>33030</v>
       </c>
       <c r="D14" s="10">
-        <v>33000</v>
+        <v>36000</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="12"/>
@@ -1117,15 +1117,15 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C15" s="10">
-        <v>30040</v>
+        <v>32962</v>
       </c>
       <c r="D15" s="10">
-        <v>33000</v>
-      </c>
-      <c r="E15" s="8"/>
+        <v>36000</v>
+      </c>
+      <c r="E15" s="3"/>
       <c r="F15" s="12"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
@@ -1135,10 +1135,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C16" s="10">
-        <v>29966</v>
+        <v>30071</v>
       </c>
       <c r="D16" s="10">
         <v>33000</v>
@@ -1273,13 +1273,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="C24" s="10">
-        <v>24030</v>
+        <v>26815</v>
       </c>
       <c r="D24" s="10">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="12"/>
@@ -1291,10 +1291,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="C25" s="10">
-        <v>23891</v>
+        <v>24030</v>
       </c>
       <c r="D25" s="10">
         <v>27000</v>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8292FBB9-6549-1047-BEEC-8DAC3E841875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8045E0DC-C9F3-6140-B692-2A51C152415A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1291,16 +1291,14 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="C25" s="10">
-        <v>24030</v>
+        <v>26753</v>
       </c>
       <c r="D25" s="10">
-        <v>27000</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="12"/>
+        <v>30000</v>
+      </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
     </row>
@@ -1309,14 +1307,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="C26" s="10">
-        <v>23812</v>
+        <v>24030</v>
       </c>
       <c r="D26" s="10">
         <v>27000</v>
       </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="12"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
@@ -1325,10 +1325,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C27" s="10">
-        <v>23750</v>
+        <v>23812</v>
       </c>
       <c r="D27" s="10">
         <v>27000</v>
@@ -1958,8 +1958,8 @@
       <c r="A64" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F54">
-    <sortCondition descending="1" ref="C2:C54"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B6:F54">
+    <sortCondition descending="1" ref="C6:C54"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8045E0DC-C9F3-6140-B692-2A51C152415A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B074621-4044-DD48-B15E-33C126E811DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="78">
   <si>
     <t>No.</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>ND17NFGP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next Major Service </t>
   </si>
 </sst>
 </file>
@@ -276,7 +279,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -318,14 +321,6 @@
     <font>
       <b/>
       <sz val="20"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -353,7 +348,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -390,8 +385,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -425,12 +426,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -445,10 +455,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -460,17 +467,17 @@
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -482,7 +489,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -491,7 +498,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -502,6 +509,17 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -842,9 +860,9 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="27" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="48.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.83203125" bestFit="1" customWidth="1"/>
@@ -859,54 +877,53 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="3"/>
-      <c r="F1" s="12"/>
+      <c r="F1" s="11"/>
       <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="20"/>
+      <c r="H1" s="19"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="11">
-        <v>45003</v>
-      </c>
-      <c r="D2" s="11">
+      <c r="B2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="10">
+        <v>45073</v>
+      </c>
+      <c r="D2" s="10">
         <v>48000</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="12"/>
+      <c r="E2" s="25"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="20"/>
+      <c r="H2" s="19"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="11">
-        <v>44969</v>
-      </c>
-      <c r="D3" s="11">
+      <c r="B3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="10">
+        <v>45003</v>
+      </c>
+      <c r="D3" s="10">
         <v>48000</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="17" t="s">
+      <c r="E3" s="25"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="16" t="s">
         <v>6</v>
       </c>
     </row>
@@ -914,21 +931,19 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="11">
-        <v>44912</v>
-      </c>
-      <c r="D4" s="11">
+      <c r="B4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="10">
+        <v>44969</v>
+      </c>
+      <c r="D4" s="10">
         <v>48000</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="G4" s="18"/>
-      <c r="H4" s="19" t="s">
+      <c r="E4" s="25"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="18" t="s">
         <v>64</v>
       </c>
     </row>
@@ -936,19 +951,21 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="11">
-        <v>44806</v>
-      </c>
-      <c r="D5" s="11">
+      <c r="B5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="10">
+        <v>44912</v>
+      </c>
+      <c r="D5" s="10">
         <v>48000</v>
       </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="22" t="s">
+      <c r="E5" s="25"/>
+      <c r="F5" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="20"/>
+      <c r="H5" s="21" t="s">
         <v>50</v>
       </c>
     </row>
@@ -956,18 +973,19 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="11">
-        <v>42073</v>
-      </c>
-      <c r="D6" s="11">
-        <v>45000</v>
-      </c>
-      <c r="E6" s="6"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="17" t="s">
+      <c r="B6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="10">
+        <v>44806</v>
+      </c>
+      <c r="D6" s="10">
+        <v>48000</v>
+      </c>
+      <c r="E6" s="25"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="16" t="s">
         <v>9</v>
       </c>
     </row>
@@ -975,33 +993,37 @@
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="10">
         <v>41964</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <v>45000</v>
       </c>
       <c r="E7" s="3"/>
-      <c r="F7" s="12"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="29" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <v>41702</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="10">
         <v>45000</v>
       </c>
       <c r="E8" s="3"/>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="11" t="s">
         <v>63</v>
       </c>
       <c r="G8" s="4"/>
@@ -1011,17 +1033,17 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="25">
-        <v>36063</v>
-      </c>
-      <c r="D9" s="25">
-        <v>39000</v>
-      </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="12"/>
+      <c r="C9" s="24">
+        <v>38987</v>
+      </c>
+      <c r="D9" s="24">
+        <v>42000</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="11"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
@@ -1029,17 +1051,17 @@
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="24">
         <v>35951</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="24">
         <v>39000</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="12"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="11"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
@@ -1048,13 +1070,14 @@
       <c r="B11" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="9">
         <v>33240</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>36000</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="E11" s="26"/>
+      <c r="F11" s="11" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1065,14 +1088,14 @@
       <c r="B12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="9">
         <v>33048</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <v>36000</v>
       </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="12"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="11"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
@@ -1083,14 +1106,14 @@
       <c r="B13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="9">
         <v>33043</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <v>36000</v>
       </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="12"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="11"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
@@ -1101,14 +1124,14 @@
       <c r="B14" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="9">
         <v>33030</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <v>36000</v>
       </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="12"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="11"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
@@ -1119,14 +1142,14 @@
       <c r="B15" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="9">
         <v>32962</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="9">
         <v>36000</v>
       </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="12"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="11"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
@@ -1135,16 +1158,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="10">
-        <v>30071</v>
-      </c>
-      <c r="D16" s="10">
-        <v>33000</v>
-      </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="12"/>
+        <v>39</v>
+      </c>
+      <c r="C16" s="9">
+        <v>32937</v>
+      </c>
+      <c r="D16" s="9">
+        <v>36000</v>
+      </c>
+      <c r="E16" s="27"/>
+      <c r="F16" s="11"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
@@ -1153,32 +1176,32 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="10">
-        <v>29848</v>
-      </c>
-      <c r="D17" s="10">
+        <v>43</v>
+      </c>
+      <c r="C17" s="9">
+        <v>30071</v>
+      </c>
+      <c r="D17" s="9">
         <v>33000</v>
       </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="12"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="11"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="10">
-        <v>29818</v>
-      </c>
-      <c r="D18" s="10">
+        <v>41</v>
+      </c>
+      <c r="C18" s="9">
+        <v>29848</v>
+      </c>
+      <c r="D18" s="9">
         <v>33000</v>
       </c>
-      <c r="E18" s="8"/>
-      <c r="F18" s="12"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="11"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
@@ -1189,10 +1212,10 @@
       <c r="B19" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <v>27114</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="9">
         <v>30000</v>
       </c>
     </row>
@@ -1203,14 +1226,14 @@
       <c r="B20" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="9">
         <v>26978</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <v>30000</v>
       </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="12"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="11"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
@@ -1221,14 +1244,14 @@
       <c r="B21" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="9">
         <v>26948</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <v>30000</v>
       </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="12"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="11"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
     </row>
@@ -1239,14 +1262,14 @@
       <c r="B22" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="9">
         <v>26924</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="9">
         <v>30000</v>
       </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="12"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="11"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
@@ -1257,14 +1280,14 @@
       <c r="B23" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="9">
         <v>26817</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="9">
         <v>30000</v>
       </c>
-      <c r="E23" s="8"/>
-      <c r="F23" s="12"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="11"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
@@ -1275,14 +1298,14 @@
       <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="9">
         <v>26815</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="9">
         <v>30000</v>
       </c>
       <c r="E24" s="3"/>
-      <c r="F24" s="12"/>
+      <c r="F24" s="11"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
@@ -1293,10 +1316,10 @@
       <c r="B25" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="9">
         <v>26753</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="9">
         <v>30000</v>
       </c>
       <c r="G25" s="4"/>
@@ -1307,16 +1330,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="10">
-        <v>24030</v>
-      </c>
-      <c r="D26" s="10">
+        <v>44</v>
+      </c>
+      <c r="C26" s="9">
+        <v>24153</v>
+      </c>
+      <c r="D26" s="9">
         <v>27000</v>
       </c>
       <c r="E26" s="3"/>
-      <c r="F26" s="12"/>
+      <c r="F26" s="11"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
@@ -1325,14 +1348,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="10">
-        <v>23812</v>
-      </c>
-      <c r="D27" s="10">
+        <v>52</v>
+      </c>
+      <c r="C27" s="9">
+        <v>24046</v>
+      </c>
+      <c r="D27" s="9">
         <v>27000</v>
       </c>
+      <c r="E27" s="7"/>
+      <c r="F27" s="11"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
@@ -1341,16 +1366,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" s="10">
-        <v>21242</v>
-      </c>
-      <c r="D28" s="10">
-        <v>24000</v>
-      </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="12"/>
+        <v>59</v>
+      </c>
+      <c r="C28" s="9">
+        <v>24030</v>
+      </c>
+      <c r="D28" s="9">
+        <v>27000</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="11"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
     </row>
@@ -1359,16 +1384,14 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="10">
-        <v>21103</v>
-      </c>
-      <c r="D29" s="10">
-        <v>24000</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="12"/>
+        <v>17</v>
+      </c>
+      <c r="C29" s="9">
+        <v>23812</v>
+      </c>
+      <c r="D29" s="9">
+        <v>27000</v>
+      </c>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
     </row>
@@ -1377,16 +1400,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="10">
-        <v>21044</v>
-      </c>
-      <c r="D30" s="10">
+        <v>8</v>
+      </c>
+      <c r="C30" s="9">
+        <v>21103</v>
+      </c>
+      <c r="D30" s="9">
         <v>24000</v>
       </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="12"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="11"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
     </row>
@@ -1397,14 +1420,14 @@
       <c r="B31" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="9">
         <v>20932</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="9">
         <v>24000</v>
       </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="12"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="11"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
     </row>
@@ -1415,13 +1438,13 @@
       <c r="B32" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="9">
         <v>20854</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="9">
         <v>24000</v>
       </c>
-      <c r="E32" s="3"/>
+      <c r="E32" s="25"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
@@ -1430,14 +1453,14 @@
       <c r="B33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="9">
         <v>17993</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="9">
         <v>21000</v>
       </c>
-      <c r="E33" s="8"/>
-      <c r="F33" s="12"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="11"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
@@ -1448,10 +1471,10 @@
       <c r="B34" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="10">
+      <c r="C34" s="9">
         <v>17984</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="9">
         <v>21000</v>
       </c>
       <c r="E34" s="3"/>
@@ -1465,14 +1488,14 @@
       <c r="B35" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C35" s="10">
+      <c r="C35" s="9">
         <v>17906</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D35" s="9">
         <v>21000</v>
       </c>
       <c r="E35" s="3"/>
-      <c r="F35" s="12"/>
+      <c r="F35" s="11"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
     </row>
@@ -1483,10 +1506,10 @@
       <c r="B36" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C36" s="10">
+      <c r="C36" s="9">
         <v>17822</v>
       </c>
-      <c r="D36" s="10">
+      <c r="D36" s="9">
         <v>21000</v>
       </c>
       <c r="E36" s="3"/>
@@ -1500,14 +1523,14 @@
       <c r="B37" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="10">
+      <c r="C37" s="9">
         <v>15153</v>
       </c>
-      <c r="D37" s="10">
+      <c r="D37" s="9">
         <v>18000</v>
       </c>
-      <c r="E37" s="8"/>
-      <c r="F37" s="12"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="11"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
@@ -1518,10 +1541,10 @@
       <c r="B38" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C38" s="10">
+      <c r="C38" s="9">
         <v>15070</v>
       </c>
-      <c r="D38" s="10">
+      <c r="D38" s="9">
         <v>18000</v>
       </c>
       <c r="G38" s="4"/>
@@ -1534,14 +1557,14 @@
       <c r="B39" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C39" s="10">
+      <c r="C39" s="9">
         <v>14692</v>
       </c>
-      <c r="D39" s="10">
+      <c r="D39" s="9">
         <v>18000</v>
       </c>
       <c r="E39" s="3"/>
-      <c r="F39" s="12"/>
+      <c r="F39" s="11"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
@@ -1552,10 +1575,10 @@
       <c r="B40" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="10">
+      <c r="C40" s="9">
         <v>12074</v>
       </c>
-      <c r="D40" s="10">
+      <c r="D40" s="9">
         <v>15000</v>
       </c>
       <c r="G40" s="4"/>
@@ -1568,14 +1591,14 @@
       <c r="B41" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C41" s="10">
+      <c r="C41" s="9">
         <v>11897</v>
       </c>
-      <c r="D41" s="10">
+      <c r="D41" s="9">
         <v>15000</v>
       </c>
-      <c r="E41" s="8"/>
-      <c r="F41" s="12"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="11"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
@@ -1586,14 +1609,14 @@
       <c r="B42" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="10">
+      <c r="C42" s="9">
         <v>8977</v>
       </c>
-      <c r="D42" s="10">
+      <c r="D42" s="9">
         <v>12000</v>
       </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="12"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="11"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
     </row>
@@ -1604,12 +1627,13 @@
       <c r="B43" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C43" s="10">
+      <c r="C43" s="9">
         <v>8944</v>
       </c>
-      <c r="D43" s="10">
+      <c r="D43" s="9">
         <v>12000</v>
       </c>
+      <c r="E43" s="26"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>
@@ -1620,10 +1644,10 @@
       <c r="B44" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C44" s="10">
+      <c r="C44" s="9">
         <v>5970</v>
       </c>
-      <c r="D44" s="10">
+      <c r="D44" s="9">
         <v>9000</v>
       </c>
       <c r="G44" s="4"/>
@@ -1636,10 +1660,10 @@
       <c r="B45" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C45" s="10">
+      <c r="C45" s="9">
         <v>3008</v>
       </c>
-      <c r="D45" s="10">
+      <c r="D45" s="9">
         <v>6000</v>
       </c>
       <c r="G45" s="4"/>
@@ -1652,10 +1676,10 @@
       <c r="B46" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C46" s="10">
+      <c r="C46" s="9">
         <v>0</v>
       </c>
-      <c r="D46" s="10">
+      <c r="D46" s="9">
         <v>1000</v>
       </c>
       <c r="G46" s="4"/>
@@ -1668,10 +1692,10 @@
       <c r="B47" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C47" s="10">
+      <c r="C47" s="9">
         <v>0</v>
       </c>
-      <c r="D47" s="10">
+      <c r="D47" s="9">
         <v>1000</v>
       </c>
       <c r="G47" s="4"/>
@@ -1684,10 +1708,10 @@
       <c r="B48" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C48" s="10">
+      <c r="C48" s="9">
         <v>0</v>
       </c>
-      <c r="D48" s="10">
+      <c r="D48" s="9">
         <v>1000</v>
       </c>
       <c r="G48" s="4"/>
@@ -1700,10 +1724,10 @@
       <c r="B49" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C49" s="10">
+      <c r="C49" s="9">
         <v>0</v>
       </c>
-      <c r="D49" s="10">
+      <c r="D49" s="9">
         <v>1000</v>
       </c>
       <c r="G49" s="4"/>
@@ -1716,10 +1740,10 @@
       <c r="B50" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C50" s="10">
+      <c r="C50" s="9">
         <v>0</v>
       </c>
-      <c r="D50" s="10">
+      <c r="D50" s="9">
         <v>1000</v>
       </c>
       <c r="G50" s="4"/>
@@ -1732,10 +1756,10 @@
       <c r="B51" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C51" s="10">
+      <c r="C51" s="9">
         <v>0</v>
       </c>
-      <c r="D51" s="10">
+      <c r="D51" s="9">
         <v>1000</v>
       </c>
       <c r="G51" s="4"/>
@@ -1748,10 +1772,10 @@
       <c r="B52" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C52" s="10">
+      <c r="C52" s="9">
         <v>0</v>
       </c>
-      <c r="D52" s="10">
+      <c r="D52" s="9">
         <v>1000</v>
       </c>
       <c r="G52" s="4"/>
@@ -1764,10 +1788,10 @@
       <c r="B53" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C53" s="10">
+      <c r="C53" s="9">
         <v>0</v>
       </c>
-      <c r="D53" s="10">
+      <c r="D53" s="9">
         <v>1000</v>
       </c>
       <c r="G53" s="4"/>
@@ -1780,10 +1804,10 @@
       <c r="B54" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C54" s="10">
+      <c r="C54" s="9">
         <v>0</v>
       </c>
-      <c r="D54" s="10">
+      <c r="D54" s="9">
         <v>1000</v>
       </c>
       <c r="G54" s="4"/>
@@ -1793,13 +1817,13 @@
       <c r="A55" s="2">
         <v>54</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C55" s="15">
+      <c r="C55" s="14">
         <v>60031</v>
       </c>
-      <c r="D55" s="15">
+      <c r="D55" s="14">
         <v>63000</v>
       </c>
       <c r="E55" s="3" t="s">
@@ -1813,13 +1837,13 @@
       <c r="A56" s="2">
         <v>55</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B56" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C56" s="15">
+      <c r="C56" s="14">
         <v>56725</v>
       </c>
-      <c r="D56" s="15">
+      <c r="D56" s="14">
         <v>60000</v>
       </c>
       <c r="E56" s="3" t="s">
@@ -1830,13 +1854,13 @@
       <c r="A57" s="2">
         <v>56</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="B57" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C57" s="15">
+      <c r="C57" s="14">
         <v>53997</v>
       </c>
-      <c r="D57" s="15">
+      <c r="D57" s="14">
         <v>57000</v>
       </c>
       <c r="E57" s="3" t="s">
@@ -1847,13 +1871,13 @@
       <c r="A58" s="2">
         <v>57</v>
       </c>
-      <c r="B58" s="14" t="s">
+      <c r="B58" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C58" s="15">
+      <c r="C58" s="14">
         <v>51012</v>
       </c>
-      <c r="D58" s="15">
+      <c r="D58" s="14">
         <v>54000</v>
       </c>
       <c r="E58" s="3" t="s">
@@ -1864,55 +1888,55 @@
       <c r="A59" s="2">
         <v>58</v>
       </c>
-      <c r="B59" s="14" t="s">
+      <c r="B59" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C59" s="15">
+      <c r="C59" s="14">
         <v>51007</v>
       </c>
-      <c r="D59" s="15">
+      <c r="D59" s="14">
         <v>54000</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F59" s="12"/>
+      <c r="F59" s="11"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>59</v>
       </c>
-      <c r="B60" s="14" t="s">
+      <c r="B60" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C60" s="15">
+      <c r="C60" s="14">
         <v>51002</v>
       </c>
-      <c r="D60" s="15">
+      <c r="D60" s="14">
         <v>54000</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F60" s="12"/>
+      <c r="F60" s="11"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>60</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="B61" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C61" s="15">
+      <c r="C61" s="14">
         <v>50855</v>
       </c>
-      <c r="D61" s="15">
+      <c r="D61" s="14">
         <v>54000</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F61" s="12" t="s">
+      <c r="F61" s="11" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1920,37 +1944,37 @@
       <c r="A62" s="2">
         <v>61</v>
       </c>
-      <c r="B62" s="14" t="s">
+      <c r="B62" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C62" s="15">
+      <c r="C62" s="14">
         <v>44849</v>
       </c>
-      <c r="D62" s="15">
+      <c r="D62" s="14">
         <v>48000</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F62" s="12"/>
+      <c r="F62" s="11"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>62</v>
       </c>
-      <c r="B63" s="14" t="s">
+      <c r="B63" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C63" s="15">
+      <c r="C63" s="14">
         <v>982</v>
       </c>
-      <c r="D63" s="15">
+      <c r="D63" s="14">
         <v>3000</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F63" s="13" t="s">
+      <c r="F63" s="12" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1958,8 +1982,8 @@
       <c r="A64" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B6:F54">
-    <sortCondition descending="1" ref="C6:C54"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F54">
+    <sortCondition descending="1" ref="C2:C54"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B074621-4044-DD48-B15E-33C126E811DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02021959-49BE-8C4C-83B5-078AA73C0317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="77">
   <si>
     <t>No.</t>
   </si>
@@ -266,9 +266,6 @@
   </si>
   <si>
     <t>ND17NFGP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Next Major Service </t>
   </si>
 </sst>
 </file>
@@ -279,7 +276,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -347,8 +344,16 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -382,12 +387,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +439,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -510,15 +509,10 @@
     <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -903,7 +897,7 @@
       <c r="D2" s="10">
         <v>48000</v>
       </c>
-      <c r="E2" s="25"/>
+      <c r="E2" s="3"/>
       <c r="G2" s="2"/>
       <c r="H2" s="19"/>
     </row>
@@ -920,7 +914,7 @@
       <c r="D3" s="10">
         <v>48000</v>
       </c>
-      <c r="E3" s="25"/>
+      <c r="E3" s="3"/>
       <c r="F3" s="11"/>
       <c r="G3" s="15"/>
       <c r="H3" s="16" t="s">
@@ -940,7 +934,7 @@
       <c r="D4" s="10">
         <v>48000</v>
       </c>
-      <c r="E4" s="25"/>
+      <c r="E4" s="3"/>
       <c r="F4" s="11"/>
       <c r="G4" s="17"/>
       <c r="H4" s="18" t="s">
@@ -960,7 +954,7 @@
       <c r="D5" s="10">
         <v>48000</v>
       </c>
-      <c r="E5" s="25"/>
+      <c r="E5" s="3"/>
       <c r="F5" s="11" t="s">
         <v>67</v>
       </c>
@@ -982,7 +976,7 @@
       <c r="D6" s="10">
         <v>48000</v>
       </c>
-      <c r="E6" s="25"/>
+      <c r="E6" s="3"/>
       <c r="F6" s="11"/>
       <c r="G6" s="22"/>
       <c r="H6" s="16" t="s">
@@ -1004,10 +998,8 @@
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="29" t="s">
-        <v>77</v>
-      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="25"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
@@ -1052,10 +1044,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C10" s="24">
-        <v>35951</v>
+        <v>35995</v>
       </c>
       <c r="D10" s="24">
         <v>39000</v>
@@ -1067,34 +1059,32 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="9">
-        <v>33240</v>
-      </c>
-      <c r="D11" s="9">
-        <v>36000</v>
-      </c>
-      <c r="E11" s="26"/>
-      <c r="F11" s="11" t="s">
-        <v>66</v>
-      </c>
+      <c r="B11" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="24">
+        <v>35951</v>
+      </c>
+      <c r="D11" s="24">
+        <v>39000</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="11"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C12" s="9">
-        <v>33048</v>
+        <v>33240</v>
       </c>
       <c r="D12" s="9">
         <v>36000</v>
       </c>
-      <c r="E12" s="25"/>
+      <c r="E12" s="3"/>
       <c r="F12" s="11"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
@@ -1104,16 +1094,18 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C13" s="9">
-        <v>33043</v>
+        <v>33048</v>
       </c>
       <c r="D13" s="9">
         <v>36000</v>
       </c>
-      <c r="E13" s="27"/>
-      <c r="F13" s="11"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="11" t="s">
+        <v>66</v>
+      </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
@@ -1122,15 +1114,15 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C14" s="9">
-        <v>33030</v>
+        <v>33043</v>
       </c>
       <c r="D14" s="9">
         <v>36000</v>
       </c>
-      <c r="E14" s="27"/>
+      <c r="E14" s="3"/>
       <c r="F14" s="11"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
@@ -1140,15 +1132,15 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C15" s="9">
-        <v>32962</v>
+        <v>33030</v>
       </c>
       <c r="D15" s="9">
         <v>36000</v>
       </c>
-      <c r="E15" s="25"/>
+      <c r="E15" s="26"/>
       <c r="F15" s="11"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
@@ -1158,15 +1150,15 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C16" s="9">
-        <v>32937</v>
+        <v>32962</v>
       </c>
       <c r="D16" s="9">
         <v>36000</v>
       </c>
-      <c r="E16" s="27"/>
+      <c r="E16" s="3"/>
       <c r="F16" s="11"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
@@ -1176,15 +1168,15 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C17" s="9">
-        <v>30071</v>
+        <v>32937</v>
       </c>
       <c r="D17" s="9">
-        <v>33000</v>
-      </c>
-      <c r="E17" s="7"/>
+        <v>36000</v>
+      </c>
+      <c r="E17" s="3"/>
       <c r="F17" s="11"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
@@ -1408,7 +1400,7 @@
       <c r="D30" s="9">
         <v>24000</v>
       </c>
-      <c r="E30" s="25"/>
+      <c r="E30" s="3"/>
       <c r="F30" s="11"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
@@ -1426,7 +1418,7 @@
       <c r="D31" s="9">
         <v>24000</v>
       </c>
-      <c r="E31" s="25"/>
+      <c r="E31" s="3"/>
       <c r="F31" s="11"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
@@ -1444,7 +1436,7 @@
       <c r="D32" s="9">
         <v>24000</v>
       </c>
-      <c r="E32" s="25"/>
+      <c r="E32" s="3"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
@@ -1615,7 +1607,7 @@
       <c r="D42" s="9">
         <v>12000</v>
       </c>
-      <c r="E42" s="27"/>
+      <c r="E42" s="3"/>
       <c r="F42" s="11"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -1633,7 +1625,7 @@
       <c r="D43" s="9">
         <v>12000</v>
       </c>
-      <c r="E43" s="26"/>
+      <c r="E43" s="3"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>
@@ -1674,13 +1666,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C46" s="9">
-        <v>0</v>
+        <v>1019</v>
       </c>
       <c r="D46" s="9">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -1690,13 +1682,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C47" s="9">
-        <v>0</v>
+        <v>1006</v>
       </c>
       <c r="D47" s="9">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
@@ -1706,7 +1698,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C48" s="9">
         <v>0</v>
@@ -1722,7 +1714,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C49" s="9">
         <v>0</v>
@@ -1738,7 +1730,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C50" s="9">
         <v>0</v>
@@ -1754,7 +1746,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C51" s="9">
         <v>0</v>
@@ -1770,7 +1762,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C52" s="9">
         <v>0</v>
@@ -1786,7 +1778,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C53" s="9">
         <v>0</v>
@@ -1802,7 +1794,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C54" s="9">
         <v>0</v>
@@ -1982,8 +1974,8 @@
       <c r="A64" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F54">
-    <sortCondition descending="1" ref="C2:C54"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F18">
+    <sortCondition descending="1" ref="C5:C18"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02021959-49BE-8C4C-83B5-078AA73C0317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F1626E-5FFF-B14F-A520-05F1240F4319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -889,15 +889,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C2" s="10">
-        <v>45073</v>
+        <v>47926</v>
       </c>
       <c r="D2" s="10">
-        <v>48000</v>
+        <v>51000</v>
       </c>
       <c r="E2" s="3"/>
+      <c r="F2" s="11"/>
       <c r="G2" s="2"/>
       <c r="H2" s="19"/>
     </row>
@@ -906,16 +907,15 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C3" s="10">
-        <v>45003</v>
+        <v>45073</v>
       </c>
       <c r="D3" s="10">
         <v>48000</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="F3" s="11"/>
       <c r="G3" s="15"/>
       <c r="H3" s="16" t="s">
         <v>6</v>
@@ -926,10 +926,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C4" s="10">
-        <v>44969</v>
+        <v>45003</v>
       </c>
       <c r="D4" s="10">
         <v>48000</v>
@@ -1666,10 +1666,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C46" s="9">
-        <v>1019</v>
+        <v>1100</v>
       </c>
       <c r="D46" s="9">
         <v>3000</v>
@@ -1682,10 +1682,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C47" s="9">
-        <v>1006</v>
+        <v>1019</v>
       </c>
       <c r="D47" s="9">
         <v>3000</v>
@@ -1698,13 +1698,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C48" s="9">
-        <v>0</v>
+        <v>1006</v>
       </c>
       <c r="D48" s="9">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
@@ -1714,7 +1714,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C49" s="9">
         <v>0</v>
@@ -1730,7 +1730,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C50" s="9">
         <v>0</v>
@@ -1746,7 +1746,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C51" s="9">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C52" s="9">
         <v>0</v>
@@ -1778,7 +1778,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C53" s="9">
         <v>0</v>
@@ -1974,8 +1974,8 @@
       <c r="A64" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:F18">
-    <sortCondition descending="1" ref="C5:C18"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B43:F54">
+    <sortCondition descending="1" ref="C43:C54"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F1626E-5FFF-B14F-A520-05F1240F4319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9742E72-5995-5B4E-86D8-2B13F8299305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1717,10 +1717,10 @@
         <v>68</v>
       </c>
       <c r="C49" s="9">
-        <v>0</v>
+        <v>889</v>
       </c>
       <c r="D49" s="9">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9742E72-5995-5B4E-86D8-2B13F8299305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB7D047-78E9-9347-94DC-42F70EA0636C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1682,10 +1682,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C47" s="9">
-        <v>1019</v>
+        <v>1059</v>
       </c>
       <c r="D47" s="9">
         <v>3000</v>
@@ -1698,10 +1698,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C48" s="9">
-        <v>1006</v>
+        <v>1019</v>
       </c>
       <c r="D48" s="9">
         <v>3000</v>
@@ -1714,10 +1714,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C49" s="9">
-        <v>889</v>
+        <v>1006</v>
       </c>
       <c r="D49" s="9">
         <v>3000</v>
@@ -1730,13 +1730,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C50" s="9">
-        <v>0</v>
+        <v>889</v>
       </c>
       <c r="D50" s="9">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
@@ -1746,7 +1746,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C51" s="9">
         <v>0</v>
@@ -1974,8 +1974,8 @@
       <c r="A64" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B43:F54">
-    <sortCondition descending="1" ref="C43:C54"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B40:F52">
+    <sortCondition descending="1" ref="C40:C52"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB7D047-78E9-9347-94DC-42F70EA0636C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE602FB-7A68-474A-A38A-F795F4AEC4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1581,16 +1581,15 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C41" s="9">
-        <v>11897</v>
+        <v>11920</v>
       </c>
       <c r="D41" s="9">
         <v>15000</v>
       </c>
-      <c r="E41" s="7"/>
-      <c r="F41" s="11"/>
+      <c r="E41" s="3"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
     </row>
@@ -1599,15 +1598,15 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C42" s="9">
-        <v>8977</v>
+        <v>11897</v>
       </c>
       <c r="D42" s="9">
-        <v>12000</v>
-      </c>
-      <c r="E42" s="3"/>
+        <v>15000</v>
+      </c>
+      <c r="E42" s="7"/>
       <c r="F42" s="11"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -1617,15 +1616,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C43" s="9">
-        <v>8944</v>
+        <v>8977</v>
       </c>
       <c r="D43" s="9">
         <v>12000</v>
       </c>
       <c r="E43" s="3"/>
+      <c r="F43" s="11"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
     </row>
@@ -1974,8 +1974,8 @@
       <c r="A64" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B40:F52">
-    <sortCondition descending="1" ref="C40:C52"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B34:F43">
+    <sortCondition descending="1" ref="C34:C43"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE602FB-7A68-474A-A38A-F795F4AEC4EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB3EC49-3C68-B74F-87ED-51C97D733DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1216,15 +1216,15 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="C20" s="9">
-        <v>26978</v>
+        <v>27088</v>
       </c>
       <c r="D20" s="9">
         <v>30000</v>
       </c>
-      <c r="E20" s="7"/>
+      <c r="E20" s="3"/>
       <c r="F20" s="11"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
@@ -1234,10 +1234,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C21" s="9">
-        <v>26948</v>
+        <v>26978</v>
       </c>
       <c r="D21" s="9">
         <v>30000</v>
@@ -1252,10 +1252,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="C22" s="9">
-        <v>26924</v>
+        <v>26948</v>
       </c>
       <c r="D22" s="9">
         <v>30000</v>
@@ -1270,10 +1270,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C23" s="9">
-        <v>26817</v>
+        <v>26924</v>
       </c>
       <c r="D23" s="9">
         <v>30000</v>
@@ -1288,15 +1288,15 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C24" s="9">
-        <v>26815</v>
+        <v>26817</v>
       </c>
       <c r="D24" s="9">
         <v>30000</v>
       </c>
-      <c r="E24" s="3"/>
+      <c r="E24" s="7"/>
       <c r="F24" s="11"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
@@ -1306,14 +1306,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C25" s="9">
-        <v>26753</v>
+        <v>26815</v>
       </c>
       <c r="D25" s="9">
         <v>30000</v>
       </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="11"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
     </row>
@@ -1322,16 +1324,14 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C26" s="9">
-        <v>24153</v>
+        <v>26753</v>
       </c>
       <c r="D26" s="9">
-        <v>27000</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="11"/>
+        <v>30000</v>
+      </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
     </row>
@@ -1340,15 +1340,15 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C27" s="9">
-        <v>24046</v>
+        <v>24153</v>
       </c>
       <c r="D27" s="9">
         <v>27000</v>
       </c>
-      <c r="E27" s="7"/>
+      <c r="E27" s="3"/>
       <c r="F27" s="11"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
@@ -1358,15 +1358,15 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C28" s="9">
-        <v>24030</v>
+        <v>24046</v>
       </c>
       <c r="D28" s="9">
         <v>27000</v>
       </c>
-      <c r="E28" s="3"/>
+      <c r="E28" s="7"/>
       <c r="F28" s="11"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
@@ -1547,16 +1547,14 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="C39" s="9">
-        <v>14692</v>
+        <v>14912</v>
       </c>
       <c r="D39" s="9">
         <v>18000</v>
       </c>
-      <c r="E39" s="3"/>
-      <c r="F39" s="11"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
@@ -1565,14 +1563,16 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C40" s="9">
-        <v>12074</v>
+        <v>14692</v>
       </c>
       <c r="D40" s="9">
-        <v>15000</v>
-      </c>
+        <v>18000</v>
+      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="11"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
     </row>
@@ -1698,10 +1698,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C48" s="9">
-        <v>1019</v>
+        <v>1045</v>
       </c>
       <c r="D48" s="9">
         <v>3000</v>
@@ -1714,10 +1714,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C49" s="9">
-        <v>1006</v>
+        <v>1019</v>
       </c>
       <c r="D49" s="9">
         <v>3000</v>
@@ -1730,10 +1730,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C50" s="9">
-        <v>889</v>
+        <v>1006</v>
       </c>
       <c r="D50" s="9">
         <v>3000</v>
@@ -1746,13 +1746,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C51" s="9">
-        <v>0</v>
+        <v>889</v>
       </c>
       <c r="D51" s="9">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -1762,7 +1762,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C52" s="9">
         <v>0</v>
@@ -1778,7 +1778,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C53" s="9">
         <v>0</v>
@@ -1974,8 +1974,8 @@
       <c r="A64" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B34:F43">
-    <sortCondition descending="1" ref="C34:C43"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B17:F29">
+    <sortCondition descending="1" ref="C17:C29"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB3EC49-3C68-B74F-87ED-51C97D733DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA7138E-9809-0A41-AAC0-1462B10AAAC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1395,10 +1395,10 @@
         <v>8</v>
       </c>
       <c r="C30" s="9">
-        <v>21103</v>
+        <v>23927</v>
       </c>
       <c r="D30" s="9">
-        <v>24000</v>
+        <v>27000</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="11"/>
@@ -1464,10 +1464,10 @@
         <v>57</v>
       </c>
       <c r="C34" s="9">
-        <v>17984</v>
+        <v>20820</v>
       </c>
       <c r="D34" s="9">
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="E34" s="3"/>
       <c r="G34" s="4"/>
@@ -1534,10 +1534,10 @@
         <v>54</v>
       </c>
       <c r="C38" s="9">
-        <v>15070</v>
+        <v>18344</v>
       </c>
       <c r="D38" s="9">
-        <v>18000</v>
+        <v>21000</v>
       </c>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA7138E-9809-0A41-AAC0-1462B10AAAC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D054921F-F323-7C48-A3DC-BBCC2112D244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1376,14 +1376,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C29" s="9">
-        <v>23812</v>
+        <v>23927</v>
       </c>
       <c r="D29" s="9">
         <v>27000</v>
       </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="11"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
     </row>
@@ -1392,16 +1394,14 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C30" s="9">
-        <v>23927</v>
+        <v>23812</v>
       </c>
       <c r="D30" s="9">
         <v>27000</v>
       </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="11"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
     </row>
@@ -1443,16 +1443,15 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C33" s="9">
-        <v>17993</v>
+        <v>20820</v>
       </c>
       <c r="D33" s="9">
-        <v>21000</v>
-      </c>
-      <c r="E33" s="7"/>
-      <c r="F33" s="11"/>
+        <v>24000</v>
+      </c>
+      <c r="E33" s="3"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
     </row>
@@ -1461,15 +1460,14 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C34" s="9">
-        <v>20820</v>
+        <v>18344</v>
       </c>
       <c r="D34" s="9">
-        <v>24000</v>
-      </c>
-      <c r="E34" s="3"/>
+        <v>21000</v>
+      </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
     </row>
@@ -1478,15 +1476,15 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C35" s="9">
-        <v>17906</v>
+        <v>17993</v>
       </c>
       <c r="D35" s="9">
         <v>21000</v>
       </c>
-      <c r="E35" s="3"/>
+      <c r="E35" s="7"/>
       <c r="F35" s="11"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
@@ -1496,15 +1494,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C36" s="9">
-        <v>17822</v>
+        <v>17906</v>
       </c>
       <c r="D36" s="9">
         <v>21000</v>
       </c>
       <c r="E36" s="3"/>
+      <c r="F36" s="11"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
     </row>
@@ -1513,16 +1512,15 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="C37" s="9">
-        <v>15153</v>
+        <v>17822</v>
       </c>
       <c r="D37" s="9">
-        <v>18000</v>
-      </c>
-      <c r="E37" s="7"/>
-      <c r="F37" s="11"/>
+        <v>21000</v>
+      </c>
+      <c r="E37" s="3"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
     </row>
@@ -1531,14 +1529,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C38" s="9">
-        <v>18344</v>
+        <v>15153</v>
       </c>
       <c r="D38" s="9">
-        <v>21000</v>
-      </c>
+        <v>18000</v>
+      </c>
+      <c r="E38" s="7"/>
+      <c r="F38" s="11"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
     </row>
@@ -1974,8 +1974,8 @@
       <c r="A64" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B17:F29">
-    <sortCondition descending="1" ref="C17:C29"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F54">
+    <sortCondition descending="1" ref="C2:C54"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D054921F-F323-7C48-A3DC-BBCC2112D244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD6A7FB-14B3-634F-82BC-7E697F1B0BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="78">
   <si>
     <t>No.</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>ND17NFGP</t>
+  </si>
+  <si>
+    <t>Mounting issue/Headlight alignment is off after accident repairs</t>
   </si>
 </sst>
 </file>
@@ -889,10 +892,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C2" s="10">
-        <v>47926</v>
+        <v>48060</v>
       </c>
       <c r="D2" s="10">
         <v>51000</v>
@@ -907,15 +910,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C3" s="10">
-        <v>45073</v>
+        <v>47926</v>
       </c>
       <c r="D3" s="10">
-        <v>48000</v>
+        <v>51000</v>
       </c>
       <c r="E3" s="3"/>
+      <c r="F3" s="11"/>
       <c r="G3" s="15"/>
       <c r="H3" s="16" t="s">
         <v>6</v>
@@ -926,16 +930,15 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C4" s="10">
-        <v>45003</v>
+        <v>45073</v>
       </c>
       <c r="D4" s="10">
         <v>48000</v>
       </c>
       <c r="E4" s="3"/>
-      <c r="F4" s="11"/>
       <c r="G4" s="17"/>
       <c r="H4" s="18" t="s">
         <v>64</v>
@@ -946,18 +949,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="10">
-        <v>44912</v>
+        <v>45003</v>
       </c>
       <c r="D5" s="10">
         <v>48000</v>
       </c>
       <c r="E5" s="3"/>
-      <c r="F5" s="11" t="s">
-        <v>67</v>
-      </c>
+      <c r="F5" s="11"/>
       <c r="G5" s="20"/>
       <c r="H5" s="21" t="s">
         <v>50</v>
@@ -968,16 +969,18 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6" s="10">
-        <v>44806</v>
+        <v>44912</v>
       </c>
       <c r="D6" s="10">
         <v>48000</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="11"/>
+      <c r="F6" s="11" t="s">
+        <v>67</v>
+      </c>
       <c r="G6" s="22"/>
       <c r="H6" s="16" t="s">
         <v>9</v>
@@ -1159,7 +1162,9 @@
         <v>36000</v>
       </c>
       <c r="E16" s="3"/>
-      <c r="F16" s="11"/>
+      <c r="F16" s="11" t="s">
+        <v>77</v>
+      </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
@@ -1714,10 +1719,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C49" s="9">
-        <v>1019</v>
+        <v>1044</v>
       </c>
       <c r="D49" s="9">
         <v>3000</v>
@@ -1730,10 +1735,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C50" s="9">
-        <v>1006</v>
+        <v>1019</v>
       </c>
       <c r="D50" s="9">
         <v>3000</v>
@@ -1746,10 +1751,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C51" s="9">
-        <v>889</v>
+        <v>1011</v>
       </c>
       <c r="D51" s="9">
         <v>3000</v>
@@ -1762,13 +1767,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C52" s="9">
-        <v>0</v>
+        <v>1006</v>
       </c>
       <c r="D52" s="9">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
@@ -1778,13 +1783,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C53" s="9">
-        <v>0</v>
+        <v>889</v>
       </c>
       <c r="D53" s="9">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -1794,7 +1799,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C54" s="9">
         <v>0</v>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD6A7FB-14B3-634F-82BC-7E697F1B0BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42FECD6F-B140-AB4D-B5D8-E26B876F18EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="79">
   <si>
     <t>No.</t>
   </si>
@@ -269,15 +269,19 @@
   </si>
   <si>
     <t>Mounting issue/Headlight alignment is off after accident repairs</t>
+  </si>
+  <si>
+    <t>Date Serviced</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -442,7 +446,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -517,6 +521,24 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -853,1134 +875,1270 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD8F41E-515C-324C-BF16-60C17361A01E}">
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="27" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="48.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="51" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" hidden="1"/>
+    <col min="3" max="3" width="21" style="32" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="48.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="51" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.83203125" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="2" t="s">
+      <c r="F1" s="3"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="19"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I1" s="19"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="28">
+        <v>46293</v>
+      </c>
+      <c r="D2" s="10">
         <v>48060</v>
       </c>
-      <c r="D2" s="10">
+      <c r="E2" s="10">
         <v>51000</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="19"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F2" s="3"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="19"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="28">
+        <v>46280</v>
+      </c>
+      <c r="D3" s="10">
         <v>47926</v>
       </c>
-      <c r="D3" s="10">
+      <c r="E3" s="10">
         <v>51000</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="16" t="s">
+      <c r="F3" s="3"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="28">
+        <v>46276</v>
+      </c>
+      <c r="D4" s="10">
         <v>45073</v>
       </c>
-      <c r="D4" s="10">
+      <c r="E4" s="10">
         <v>48000</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="18" t="s">
+      <c r="F4" s="3"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="18" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="28">
+        <v>46275</v>
+      </c>
+      <c r="D5" s="10">
         <v>45003</v>
       </c>
-      <c r="D5" s="10">
+      <c r="E5" s="10">
         <v>48000</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="21" t="s">
+      <c r="F5" s="3"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="21" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="28"/>
+      <c r="D6" s="10">
         <v>44912</v>
       </c>
-      <c r="D6" s="10">
+      <c r="E6" s="10">
         <v>48000</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="3"/>
+      <c r="G6" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G6" s="22"/>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="22"/>
+      <c r="I6" s="16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="28"/>
+      <c r="D7" s="10">
         <v>41964</v>
       </c>
-      <c r="D7" s="10">
+      <c r="E7" s="10">
         <v>45000</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="25"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F7" s="3"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="25"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="28">
+        <v>46269</v>
+      </c>
+      <c r="D8" s="10">
         <v>41702</v>
       </c>
-      <c r="D8" s="10">
+      <c r="E8" s="10">
         <v>45000</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="3"/>
+      <c r="G8" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="4"/>
       <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I8" s="4"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="29">
+        <v>46275</v>
+      </c>
+      <c r="D9" s="24">
         <v>38987</v>
       </c>
-      <c r="D9" s="24">
+      <c r="E9" s="24">
         <v>42000</v>
       </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="4"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="11"/>
       <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="29">
+        <v>46280</v>
+      </c>
+      <c r="D10" s="24">
         <v>35995</v>
       </c>
-      <c r="D10" s="24">
+      <c r="E10" s="24">
         <v>39000</v>
       </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="11"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F10" s="7"/>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="29"/>
+      <c r="D11" s="24">
         <v>35951</v>
       </c>
-      <c r="D11" s="24">
+      <c r="E11" s="24">
         <v>39000</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="11"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F11" s="7"/>
+      <c r="G11" s="11"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="30">
+        <v>46293</v>
+      </c>
+      <c r="D12" s="9">
         <v>33240</v>
       </c>
-      <c r="D12" s="9">
+      <c r="E12" s="9">
         <v>36000</v>
       </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="4"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="11"/>
       <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="30"/>
+      <c r="D13" s="9">
         <v>33048</v>
       </c>
-      <c r="D13" s="9">
+      <c r="E13" s="9">
         <v>36000</v>
       </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="3"/>
+      <c r="G13" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="4"/>
       <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I13" s="4"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="30">
+        <v>46272</v>
+      </c>
+      <c r="D14" s="9">
         <v>33043</v>
       </c>
-      <c r="D14" s="9">
+      <c r="E14" s="9">
         <v>36000</v>
       </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="4"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="11"/>
       <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I14" s="4"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="30">
+        <v>46272</v>
+      </c>
+      <c r="D15" s="9">
         <v>33030</v>
       </c>
-      <c r="D15" s="9">
+      <c r="E15" s="9">
         <v>36000</v>
       </c>
-      <c r="E15" s="26"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="4"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="11"/>
       <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="30"/>
+      <c r="D16" s="9">
         <v>32962</v>
       </c>
-      <c r="D16" s="9">
+      <c r="E16" s="9">
         <v>36000</v>
       </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="3"/>
+      <c r="G16" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G16" s="4"/>
       <c r="H16" s="4"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="30">
+        <v>46275</v>
+      </c>
+      <c r="D17" s="9">
         <v>32937</v>
       </c>
-      <c r="D17" s="9">
+      <c r="E17" s="9">
         <v>36000</v>
       </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="11"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F17" s="3"/>
+      <c r="G17" s="11"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="30"/>
+      <c r="D18" s="9">
         <v>29848</v>
       </c>
-      <c r="D18" s="9">
+      <c r="E18" s="9">
         <v>33000</v>
       </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="4"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="11"/>
       <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I18" s="4"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="30">
+        <v>46265</v>
+      </c>
+      <c r="D19" s="9">
         <v>27114</v>
       </c>
-      <c r="D19" s="9">
+      <c r="E19" s="9">
         <v>30000</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="30">
+        <v>46286</v>
+      </c>
+      <c r="D20" s="9">
         <v>27088</v>
       </c>
-      <c r="D20" s="9">
+      <c r="E20" s="9">
         <v>30000</v>
       </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="4"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="11"/>
       <c r="H20" s="4"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I20" s="4"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="30"/>
+      <c r="D21" s="9">
         <v>26978</v>
       </c>
-      <c r="D21" s="9">
+      <c r="E21" s="9">
         <v>30000</v>
       </c>
-      <c r="E21" s="7"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="4"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="11"/>
       <c r="H21" s="4"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I21" s="4"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="30"/>
+      <c r="D22" s="9">
         <v>26948</v>
       </c>
-      <c r="D22" s="9">
+      <c r="E22" s="9">
         <v>30000</v>
       </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="4"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="11"/>
       <c r="H22" s="4"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I22" s="4"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C23" s="30"/>
+      <c r="D23" s="9">
         <v>26924</v>
       </c>
-      <c r="D23" s="9">
+      <c r="E23" s="9">
         <v>30000</v>
       </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="4"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="11"/>
       <c r="H23" s="4"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I23" s="4"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="30"/>
+      <c r="D24" s="9">
         <v>26817</v>
       </c>
-      <c r="D24" s="9">
+      <c r="E24" s="9">
         <v>30000</v>
       </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="4"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="11"/>
       <c r="H24" s="4"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I24" s="4"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="30">
+        <v>46273</v>
+      </c>
+      <c r="D25" s="9">
         <v>26815</v>
       </c>
-      <c r="D25" s="9">
+      <c r="E25" s="9">
         <v>30000</v>
       </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="4"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="11"/>
       <c r="H25" s="4"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I25" s="4"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="30">
+        <v>46274</v>
+      </c>
+      <c r="D26" s="9">
         <v>26753</v>
       </c>
-      <c r="D26" s="9">
+      <c r="E26" s="9">
         <v>30000</v>
       </c>
-      <c r="G26" s="4"/>
       <c r="H26" s="4"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I26" s="4"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="30">
+        <v>46276</v>
+      </c>
+      <c r="D27" s="9">
         <v>24153</v>
       </c>
-      <c r="D27" s="9">
+      <c r="E27" s="9">
         <v>27000</v>
       </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="4"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="11"/>
       <c r="H27" s="4"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I27" s="4"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="30">
+        <v>46276</v>
+      </c>
+      <c r="D28" s="9">
         <v>24046</v>
       </c>
-      <c r="D28" s="9">
+      <c r="E28" s="9">
         <v>27000</v>
       </c>
-      <c r="E28" s="7"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="4"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="11"/>
       <c r="H28" s="4"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I28" s="4"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="30">
+        <v>46287</v>
+      </c>
+      <c r="D29" s="9">
         <v>23927</v>
       </c>
-      <c r="D29" s="9">
+      <c r="E29" s="9">
         <v>27000</v>
       </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="4"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="11"/>
       <c r="H29" s="4"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I29" s="4"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="30"/>
+      <c r="D30" s="9">
         <v>23812</v>
       </c>
-      <c r="D30" s="9">
+      <c r="E30" s="9">
         <v>27000</v>
       </c>
-      <c r="G30" s="4"/>
       <c r="H30" s="4"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I30" s="4"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="30"/>
+      <c r="D31" s="9">
         <v>20932</v>
       </c>
-      <c r="D31" s="9">
+      <c r="E31" s="9">
         <v>24000</v>
       </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="4"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="11"/>
       <c r="H31" s="4"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I31" s="4"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="30"/>
+      <c r="D32" s="9">
         <v>20854</v>
       </c>
-      <c r="D32" s="9">
+      <c r="E32" s="9">
         <v>24000</v>
       </c>
-      <c r="E32" s="3"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F32" s="3"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C33" s="30">
+        <v>46287</v>
+      </c>
+      <c r="D33" s="9">
         <v>20820</v>
       </c>
-      <c r="D33" s="9">
+      <c r="E33" s="9">
         <v>24000</v>
       </c>
-      <c r="E33" s="3"/>
-      <c r="G33" s="4"/>
+      <c r="F33" s="3"/>
       <c r="H33" s="4"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I33" s="4"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="30">
+        <v>46287</v>
+      </c>
+      <c r="D34" s="9">
         <v>18344</v>
       </c>
-      <c r="D34" s="9">
+      <c r="E34" s="9">
         <v>21000</v>
       </c>
-      <c r="G34" s="4"/>
       <c r="H34" s="4"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I34" s="4"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C35" s="9">
+      <c r="C35" s="30"/>
+      <c r="D35" s="9">
         <v>17993</v>
       </c>
-      <c r="D35" s="9">
+      <c r="E35" s="9">
         <v>21000</v>
       </c>
-      <c r="E35" s="7"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="4"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="11"/>
       <c r="H35" s="4"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I35" s="4"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="30">
+        <v>46274</v>
+      </c>
+      <c r="D36" s="9">
         <v>17906</v>
       </c>
-      <c r="D36" s="9">
+      <c r="E36" s="9">
         <v>21000</v>
       </c>
-      <c r="E36" s="3"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="4"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="11"/>
       <c r="H36" s="4"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I36" s="4"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C37" s="9">
+      <c r="C37" s="30">
+        <v>46269</v>
+      </c>
+      <c r="D37" s="9">
         <v>17822</v>
       </c>
-      <c r="D37" s="9">
+      <c r="E37" s="9">
         <v>21000</v>
       </c>
-      <c r="E37" s="3"/>
-      <c r="G37" s="4"/>
+      <c r="F37" s="3"/>
       <c r="H37" s="4"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I37" s="4"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C38" s="30"/>
+      <c r="D38" s="9">
         <v>15153</v>
       </c>
-      <c r="D38" s="9">
+      <c r="E38" s="9">
         <v>18000</v>
       </c>
-      <c r="E38" s="7"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="4"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="11"/>
       <c r="H38" s="4"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I38" s="4"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C39" s="9">
+      <c r="C39" s="30">
+        <v>46286</v>
+      </c>
+      <c r="D39" s="9">
         <v>14912</v>
       </c>
-      <c r="D39" s="9">
+      <c r="E39" s="9">
         <v>18000</v>
       </c>
-      <c r="G39" s="4"/>
       <c r="H39" s="4"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I39" s="4"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C40" s="30">
+        <v>46274</v>
+      </c>
+      <c r="D40" s="9">
         <v>14692</v>
       </c>
-      <c r="D40" s="9">
+      <c r="E40" s="9">
         <v>18000</v>
       </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="4"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="11"/>
       <c r="H40" s="4"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I40" s="4"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C41" s="9">
+      <c r="C41" s="30">
+        <v>46283</v>
+      </c>
+      <c r="D41" s="9">
         <v>11920</v>
       </c>
-      <c r="D41" s="9">
+      <c r="E41" s="9">
         <v>15000</v>
       </c>
-      <c r="E41" s="3"/>
-      <c r="G41" s="4"/>
+      <c r="F41" s="3"/>
       <c r="H41" s="4"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I41" s="4"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="30">
+        <v>46276</v>
+      </c>
+      <c r="D42" s="9">
         <v>11897</v>
       </c>
-      <c r="D42" s="9">
+      <c r="E42" s="9">
         <v>15000</v>
       </c>
-      <c r="E42" s="7"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="4"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="11"/>
       <c r="H42" s="4"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I42" s="4"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C43" s="9">
+      <c r="C43" s="30"/>
+      <c r="D43" s="9">
         <v>8977</v>
       </c>
-      <c r="D43" s="9">
+      <c r="E43" s="9">
         <v>12000</v>
       </c>
-      <c r="E43" s="3"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="4"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="11"/>
       <c r="H43" s="4"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I43" s="4"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="30">
+        <v>46266</v>
+      </c>
+      <c r="D44" s="9">
         <v>5970</v>
       </c>
-      <c r="D44" s="9">
+      <c r="E44" s="9">
         <v>9000</v>
       </c>
-      <c r="G44" s="4"/>
       <c r="H44" s="4"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I44" s="4"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C45" s="9">
+      <c r="C45" s="30"/>
+      <c r="D45" s="9">
         <v>3008</v>
       </c>
-      <c r="D45" s="9">
+      <c r="E45" s="9">
         <v>6000</v>
       </c>
-      <c r="G45" s="4"/>
       <c r="H45" s="4"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I45" s="4"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="30">
+        <v>46280</v>
+      </c>
+      <c r="D46" s="9">
         <v>1100</v>
       </c>
-      <c r="D46" s="9">
+      <c r="E46" s="9">
         <v>3000</v>
       </c>
-      <c r="G46" s="4"/>
       <c r="H46" s="4"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I46" s="4"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C47" s="9">
+      <c r="C47" s="30">
+        <v>46282</v>
+      </c>
+      <c r="D47" s="9">
         <v>1059</v>
       </c>
-      <c r="D47" s="9">
+      <c r="E47" s="9">
         <v>3000</v>
       </c>
-      <c r="G47" s="4"/>
       <c r="H47" s="4"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I47" s="4"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C48" s="30">
+        <v>46286</v>
+      </c>
+      <c r="D48" s="9">
         <v>1045</v>
       </c>
-      <c r="D48" s="9">
+      <c r="E48" s="9">
         <v>3000</v>
       </c>
-      <c r="G48" s="4"/>
       <c r="H48" s="4"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I48" s="4"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C49" s="9">
+      <c r="C49" s="30">
+        <v>46293</v>
+      </c>
+      <c r="D49" s="9">
         <v>1044</v>
       </c>
-      <c r="D49" s="9">
+      <c r="E49" s="9">
         <v>3000</v>
       </c>
-      <c r="G49" s="4"/>
       <c r="H49" s="4"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I49" s="4"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C50" s="30">
+        <v>46279</v>
+      </c>
+      <c r="D50" s="9">
         <v>1019</v>
       </c>
-      <c r="D50" s="9">
+      <c r="E50" s="9">
         <v>3000</v>
       </c>
-      <c r="G50" s="4"/>
       <c r="H50" s="4"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I50" s="4"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C51" s="9">
+      <c r="C51" s="30">
+        <v>46293</v>
+      </c>
+      <c r="D51" s="9">
         <v>1011</v>
       </c>
-      <c r="D51" s="9">
+      <c r="E51" s="9">
         <v>3000</v>
       </c>
-      <c r="G51" s="4"/>
       <c r="H51" s="4"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I51" s="4"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="30">
+        <v>46279</v>
+      </c>
+      <c r="D52" s="9">
         <v>1006</v>
       </c>
-      <c r="D52" s="9">
+      <c r="E52" s="9">
         <v>3000</v>
       </c>
-      <c r="G52" s="4"/>
       <c r="H52" s="4"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I52" s="4"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C53" s="9">
+      <c r="C53" s="30">
+        <v>46281</v>
+      </c>
+      <c r="D53" s="9">
         <v>889</v>
       </c>
-      <c r="D53" s="9">
+      <c r="E53" s="9">
         <v>3000</v>
       </c>
-      <c r="G53" s="4"/>
       <c r="H53" s="4"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I53" s="4"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C54" s="9">
+      <c r="C54" s="30"/>
+      <c r="D54" s="9">
         <v>0</v>
       </c>
-      <c r="D54" s="9">
+      <c r="E54" s="9">
         <v>1000</v>
       </c>
-      <c r="G54" s="4"/>
       <c r="H54" s="4"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I54" s="4"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>54</v>
       </c>
       <c r="B55" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C55" s="14">
+      <c r="C55" s="31"/>
+      <c r="D55" s="14">
         <v>60031</v>
       </c>
-      <c r="D55" s="14">
+      <c r="E55" s="14">
         <v>63000</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="F55" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>55</v>
       </c>
       <c r="B56" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C56" s="14">
+      <c r="C56" s="31"/>
+      <c r="D56" s="14">
         <v>56725</v>
       </c>
-      <c r="D56" s="14">
+      <c r="E56" s="14">
         <v>60000</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="F56" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>56</v>
       </c>
       <c r="B57" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C57" s="14">
+      <c r="C57" s="31"/>
+      <c r="D57" s="14">
         <v>53997</v>
       </c>
-      <c r="D57" s="14">
+      <c r="E57" s="14">
         <v>57000</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="F57" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>57</v>
       </c>
       <c r="B58" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C58" s="14">
+      <c r="C58" s="31"/>
+      <c r="D58" s="14">
         <v>51012</v>
       </c>
-      <c r="D58" s="14">
+      <c r="E58" s="14">
         <v>54000</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="F58" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>58</v>
       </c>
       <c r="B59" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C59" s="14">
+      <c r="C59" s="31"/>
+      <c r="D59" s="14">
         <v>51007</v>
       </c>
-      <c r="D59" s="14">
+      <c r="E59" s="14">
         <v>54000</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="F59" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F59" s="11"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G59" s="11"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>59</v>
       </c>
       <c r="B60" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C60" s="14">
+      <c r="C60" s="31"/>
+      <c r="D60" s="14">
         <v>51002</v>
       </c>
-      <c r="D60" s="14">
+      <c r="E60" s="14">
         <v>54000</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="F60" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F60" s="11"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G60" s="11"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>60</v>
       </c>
       <c r="B61" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C61" s="14">
+      <c r="C61" s="31"/>
+      <c r="D61" s="14">
         <v>50855</v>
       </c>
-      <c r="D61" s="14">
+      <c r="E61" s="14">
         <v>54000</v>
       </c>
-      <c r="E61" s="3" t="s">
+      <c r="F61" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F61" s="11" t="s">
+      <c r="G61" s="11" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>61</v>
       </c>
       <c r="B62" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C62" s="14">
+      <c r="C62" s="31"/>
+      <c r="D62" s="14">
         <v>44849</v>
       </c>
-      <c r="D62" s="14">
+      <c r="E62" s="14">
         <v>48000</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="F62" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F62" s="11"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G62" s="11"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>62</v>
       </c>
       <c r="B63" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C63" s="14">
+      <c r="C63" s="31"/>
+      <c r="D63" s="14">
         <v>982</v>
       </c>
-      <c r="D63" s="14">
+      <c r="E63" s="14">
         <v>3000</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="F63" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F63" s="12" t="s">
+      <c r="G63" s="12" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F54">
-    <sortCondition descending="1" ref="C2:C54"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:G54">
+    <sortCondition descending="1" ref="D2:D54"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42FECD6F-B140-AB4D-B5D8-E26B876F18EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A92E9FE-835A-634F-93F9-AFD7A354B215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -281,7 +281,7 @@
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -522,22 +522,22 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1009,7 +1009,9 @@
       <c r="B6" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="28"/>
+      <c r="C6" s="28">
+        <v>46213</v>
+      </c>
       <c r="D6" s="10">
         <v>44912</v>
       </c>
@@ -1032,7 +1034,9 @@
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="28"/>
+      <c r="C7" s="28">
+        <v>46260</v>
+      </c>
       <c r="D7" s="10">
         <v>41964</v>
       </c>
@@ -1114,7 +1118,9 @@
       <c r="B11" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="29"/>
+      <c r="C11" s="29">
+        <v>46267</v>
+      </c>
       <c r="D11" s="24">
         <v>35951</v>
       </c>
@@ -1152,7 +1158,9 @@
       <c r="B13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="30"/>
+      <c r="C13" s="30">
+        <v>46190</v>
+      </c>
       <c r="D13" s="9">
         <v>33048</v>
       </c>
@@ -1215,7 +1223,9 @@
       <c r="B16" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="30"/>
+      <c r="C16" s="30">
+        <v>46216</v>
+      </c>
       <c r="D16" s="9">
         <v>32962</v>
       </c>
@@ -1255,7 +1265,9 @@
       <c r="B18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="30"/>
+      <c r="C18" s="30">
+        <v>46258</v>
+      </c>
       <c r="D18" s="9">
         <v>29848</v>
       </c>
@@ -1312,7 +1324,9 @@
       <c r="B21" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="30"/>
+      <c r="C21" s="30">
+        <v>46254</v>
+      </c>
       <c r="D21" s="9">
         <v>26978</v>
       </c>
@@ -1331,7 +1345,9 @@
       <c r="B22" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="30"/>
+      <c r="C22" s="30">
+        <v>46248</v>
+      </c>
       <c r="D22" s="9">
         <v>26948</v>
       </c>
@@ -1350,7 +1366,9 @@
       <c r="B23" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="30"/>
+      <c r="C23" s="30">
+        <v>46204</v>
+      </c>
       <c r="D23" s="9">
         <v>26924</v>
       </c>
@@ -1369,7 +1387,9 @@
       <c r="B24" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="30"/>
+      <c r="C24" s="30">
+        <v>46248</v>
+      </c>
       <c r="D24" s="9">
         <v>26817</v>
       </c>
@@ -1426,19 +1446,18 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="C27" s="30">
-        <v>46276</v>
+        <v>46295</v>
       </c>
       <c r="D27" s="9">
-        <v>24153</v>
+        <v>26668</v>
       </c>
       <c r="E27" s="9">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="F27" s="3"/>
-      <c r="G27" s="11"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
     </row>
@@ -1447,18 +1466,18 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C28" s="30">
         <v>46276</v>
       </c>
       <c r="D28" s="9">
-        <v>24046</v>
+        <v>24153</v>
       </c>
       <c r="E28" s="9">
         <v>27000</v>
       </c>
-      <c r="F28" s="7"/>
+      <c r="F28" s="3"/>
       <c r="G28" s="11"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
@@ -1468,18 +1487,18 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="C29" s="30">
-        <v>46287</v>
+        <v>46276</v>
       </c>
       <c r="D29" s="9">
-        <v>23927</v>
+        <v>24046</v>
       </c>
       <c r="E29" s="9">
         <v>27000</v>
       </c>
-      <c r="F29" s="3"/>
+      <c r="F29" s="7"/>
       <c r="G29" s="11"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
@@ -1489,15 +1508,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" s="30"/>
+        <v>8</v>
+      </c>
+      <c r="C30" s="30">
+        <v>46287</v>
+      </c>
       <c r="D30" s="9">
-        <v>23812</v>
+        <v>23927</v>
       </c>
       <c r="E30" s="9">
         <v>27000</v>
       </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="11"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
     </row>
@@ -1506,17 +1529,17 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="30"/>
+        <v>17</v>
+      </c>
+      <c r="C31" s="30">
+        <v>46141</v>
+      </c>
       <c r="D31" s="9">
-        <v>20932</v>
+        <v>23812</v>
       </c>
       <c r="E31" s="9">
-        <v>24000</v>
-      </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="11"/>
+        <v>27000</v>
+      </c>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
     </row>
@@ -1525,29 +1548,32 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C32" s="30"/>
+        <v>56</v>
+      </c>
+      <c r="C32" s="30">
+        <v>46261</v>
+      </c>
       <c r="D32" s="9">
-        <v>20854</v>
+        <v>20932</v>
       </c>
       <c r="E32" s="9">
         <v>24000</v>
       </c>
       <c r="F32" s="3"/>
+      <c r="G32" s="11"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C33" s="30">
-        <v>46287</v>
+        <v>46252</v>
       </c>
       <c r="D33" s="9">
-        <v>20820</v>
+        <v>20854</v>
       </c>
       <c r="E33" s="9">
         <v>24000</v>
@@ -1561,17 +1587,18 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C34" s="30">
         <v>46287</v>
       </c>
       <c r="D34" s="9">
-        <v>18344</v>
+        <v>20820</v>
       </c>
       <c r="E34" s="9">
-        <v>21000</v>
-      </c>
+        <v>24000</v>
+      </c>
+      <c r="F34" s="3"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
     </row>
@@ -1580,17 +1607,17 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" s="30"/>
+        <v>54</v>
+      </c>
+      <c r="C35" s="30">
+        <v>46287</v>
+      </c>
       <c r="D35" s="9">
-        <v>17993</v>
+        <v>18344</v>
       </c>
       <c r="E35" s="9">
         <v>21000</v>
       </c>
-      <c r="F35" s="7"/>
-      <c r="G35" s="11"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
     </row>
@@ -1599,18 +1626,18 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C36" s="30">
-        <v>46274</v>
+        <v>46248</v>
       </c>
       <c r="D36" s="9">
-        <v>17906</v>
+        <v>17993</v>
       </c>
       <c r="E36" s="9">
         <v>21000</v>
       </c>
-      <c r="F36" s="3"/>
+      <c r="F36" s="7"/>
       <c r="G36" s="11"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
@@ -1620,18 +1647,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C37" s="30">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="D37" s="9">
-        <v>17822</v>
+        <v>17906</v>
       </c>
       <c r="E37" s="9">
         <v>21000</v>
       </c>
       <c r="F37" s="3"/>
+      <c r="G37" s="11"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
     </row>
@@ -1642,7 +1670,9 @@
       <c r="B38" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="30"/>
+      <c r="C38" s="30">
+        <v>46241</v>
+      </c>
       <c r="D38" s="9">
         <v>15153</v>
       </c>
@@ -1742,7 +1772,9 @@
       <c r="B43" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C43" s="30"/>
+      <c r="C43" s="30">
+        <v>46171</v>
+      </c>
       <c r="D43" s="9">
         <v>8977</v>
       </c>
@@ -1780,7 +1812,9 @@
       <c r="B45" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C45" s="30"/>
+      <c r="C45" s="30">
+        <v>46261</v>
+      </c>
       <c r="D45" s="9">
         <v>3008</v>
       </c>
@@ -2133,7 +2167,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2"/>
     </row>
   </sheetData>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A92E9FE-835A-634F-93F9-AFD7A354B215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86E6CF40-A9AC-9346-AF0D-259B69209D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1829,16 +1829,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C46" s="30">
-        <v>46280</v>
+        <v>46296</v>
       </c>
       <c r="D46" s="9">
-        <v>1100</v>
+        <v>2991</v>
       </c>
       <c r="E46" s="9">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
@@ -1848,13 +1848,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C47" s="30">
-        <v>46282</v>
+        <v>46280</v>
       </c>
       <c r="D47" s="9">
-        <v>1059</v>
+        <v>1100</v>
       </c>
       <c r="E47" s="9">
         <v>3000</v>
@@ -1867,13 +1867,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C48" s="30">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="D48" s="9">
-        <v>1045</v>
+        <v>1059</v>
       </c>
       <c r="E48" s="9">
         <v>3000</v>
@@ -1886,13 +1886,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C49" s="30">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="D49" s="9">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="E49" s="9">
         <v>3000</v>
@@ -1905,13 +1905,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C50" s="30">
-        <v>46279</v>
+        <v>46293</v>
       </c>
       <c r="D50" s="9">
-        <v>1019</v>
+        <v>1044</v>
       </c>
       <c r="E50" s="9">
         <v>3000</v>
@@ -1924,13 +1924,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C51" s="30">
-        <v>46293</v>
+        <v>46279</v>
       </c>
       <c r="D51" s="9">
-        <v>1011</v>
+        <v>1019</v>
       </c>
       <c r="E51" s="9">
         <v>3000</v>
@@ -1943,13 +1943,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C52" s="30">
-        <v>46279</v>
+        <v>46293</v>
       </c>
       <c r="D52" s="9">
-        <v>1006</v>
+        <v>1011</v>
       </c>
       <c r="E52" s="9">
         <v>3000</v>
@@ -2171,8 +2171,8 @@
       <c r="A64" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:G54">
-    <sortCondition descending="1" ref="D2:D54"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B43:G53">
+    <sortCondition descending="1" ref="D43:D53"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86E6CF40-A9AC-9346-AF0D-259B69209D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEE3C257-0DE5-F94B-8C3A-B33F2ED92D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="80">
   <si>
     <t>No.</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>Date Serviced</t>
+  </si>
+  <si>
+    <t>Needs Swing lock Vush (50353-M9Q-0000) x2 and Engine mountings x2, Link Stopper rubber (50352-ADB-0000)</t>
   </si>
 </sst>
 </file>
@@ -974,6 +977,9 @@
         <v>48000</v>
       </c>
       <c r="F4" s="3"/>
+      <c r="G4" t="s">
+        <v>79</v>
+      </c>
       <c r="H4" s="17"/>
       <c r="I4" s="18" t="s">
         <v>64</v>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEE3C257-0DE5-F94B-8C3A-B33F2ED92D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C67E589-BAC4-3E4C-9651-7AE65D489217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1819,13 +1819,13 @@
         <v>65</v>
       </c>
       <c r="C45" s="30">
-        <v>46261</v>
+        <v>46297</v>
       </c>
       <c r="D45" s="9">
-        <v>3008</v>
+        <v>5951</v>
       </c>
       <c r="E45" s="9">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
@@ -1873,13 +1873,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C48" s="30">
-        <v>46282</v>
+        <v>46297</v>
       </c>
       <c r="D48" s="9">
-        <v>1059</v>
+        <v>1098</v>
       </c>
       <c r="E48" s="9">
         <v>3000</v>
@@ -1892,13 +1892,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C49" s="30">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="D49" s="9">
-        <v>1045</v>
+        <v>1059</v>
       </c>
       <c r="E49" s="9">
         <v>3000</v>
@@ -1911,13 +1911,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C50" s="30">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="D50" s="9">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="E50" s="9">
         <v>3000</v>
@@ -1930,13 +1930,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C51" s="30">
-        <v>46279</v>
+        <v>46293</v>
       </c>
       <c r="D51" s="9">
-        <v>1019</v>
+        <v>1044</v>
       </c>
       <c r="E51" s="9">
         <v>3000</v>
@@ -1949,13 +1949,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C52" s="30">
-        <v>46293</v>
+        <v>46279</v>
       </c>
       <c r="D52" s="9">
-        <v>1011</v>
+        <v>1019</v>
       </c>
       <c r="E52" s="9">
         <v>3000</v>
@@ -1968,13 +1968,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C53" s="30">
-        <v>46281</v>
+        <v>46293</v>
       </c>
       <c r="D53" s="9">
-        <v>889</v>
+        <v>1011</v>
       </c>
       <c r="E53" s="9">
         <v>3000</v>
@@ -1987,14 +1987,16 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C54" s="30"/>
+        <v>68</v>
+      </c>
+      <c r="C54" s="30">
+        <v>46281</v>
+      </c>
       <c r="D54" s="9">
-        <v>0</v>
+        <v>889</v>
       </c>
       <c r="E54" s="9">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
@@ -2177,8 +2179,8 @@
       <c r="A64" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B43:G53">
-    <sortCondition descending="1" ref="D43:D53"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B37:G45">
+    <sortCondition descending="1" ref="D37:D45"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C67E589-BAC4-3E4C-9651-7AE65D489217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804AE2DA-3A30-E543-952F-A5ABFED871DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -235,9 +235,6 @@
     <t>MR01JHGP</t>
   </si>
   <si>
-    <t>Steering Stem was never replaced during accident repair &amp; Oil leak on the Right cover</t>
-  </si>
-  <si>
     <t>Accident repairs with a substandard touch</t>
   </si>
   <si>
@@ -275,6 +272,9 @@
   </si>
   <si>
     <t>Needs Swing lock Vush (50353-M9Q-0000) x2 and Engine mountings x2, Link Stopper rubber (50352-ADB-0000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steering Stem was never replaced during accident repair, needs Eng hanger (50351-ARA-0103) </t>
   </si>
 </sst>
 </file>
@@ -901,7 +901,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>2</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="F4" s="3"/>
       <c r="G4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H4" s="17"/>
       <c r="I4" s="18" t="s">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H6" s="22"/>
       <c r="I6" s="16" t="s">
@@ -1082,19 +1082,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="C9" s="29">
-        <v>46275</v>
+        <v>46302</v>
       </c>
       <c r="D9" s="24">
-        <v>38987</v>
+        <v>39089</v>
       </c>
       <c r="E9" s="24">
         <v>42000</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="11"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="11" t="s">
+        <v>79</v>
+      </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
     </row>
@@ -1103,16 +1105,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C10" s="29">
-        <v>46280</v>
+        <v>46275</v>
       </c>
       <c r="D10" s="24">
-        <v>35995</v>
+        <v>38987</v>
       </c>
       <c r="E10" s="24">
-        <v>39000</v>
+        <v>42000</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="11"/>
@@ -1122,13 +1124,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C11" s="29">
-        <v>46267</v>
+        <v>46280</v>
       </c>
       <c r="D11" s="24">
-        <v>35951</v>
+        <v>35995</v>
       </c>
       <c r="E11" s="24">
         <v>39000</v>
@@ -1140,19 +1142,19 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="30">
-        <v>46293</v>
-      </c>
-      <c r="D12" s="9">
-        <v>33240</v>
-      </c>
-      <c r="E12" s="9">
-        <v>36000</v>
-      </c>
-      <c r="F12" s="3"/>
+      <c r="B12" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="29">
+        <v>46267</v>
+      </c>
+      <c r="D12" s="24">
+        <v>35951</v>
+      </c>
+      <c r="E12" s="24">
+        <v>39000</v>
+      </c>
+      <c r="F12" s="7"/>
       <c r="G12" s="11"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -1162,21 +1164,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C13" s="30">
-        <v>46190</v>
+        <v>46293</v>
       </c>
       <c r="D13" s="9">
-        <v>33048</v>
+        <v>33240</v>
       </c>
       <c r="E13" s="9">
         <v>36000</v>
       </c>
       <c r="F13" s="3"/>
-      <c r="G13" s="11" t="s">
-        <v>66</v>
-      </c>
+      <c r="G13" s="11"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -1835,7 +1835,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C46" s="30">
         <v>46296</v>
@@ -1854,16 +1854,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C47" s="30">
-        <v>46280</v>
+        <v>46302</v>
       </c>
       <c r="D47" s="9">
-        <v>1100</v>
+        <v>2794</v>
       </c>
       <c r="E47" s="9">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
@@ -1873,13 +1873,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C48" s="30">
-        <v>46297</v>
+        <v>46280</v>
       </c>
       <c r="D48" s="9">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="E48" s="9">
         <v>3000</v>
@@ -1892,13 +1892,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C49" s="30">
-        <v>46282</v>
+        <v>46297</v>
       </c>
       <c r="D49" s="9">
-        <v>1059</v>
+        <v>1098</v>
       </c>
       <c r="E49" s="9">
         <v>3000</v>
@@ -1911,13 +1911,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C50" s="30">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="D50" s="9">
-        <v>1045</v>
+        <v>1059</v>
       </c>
       <c r="E50" s="9">
         <v>3000</v>
@@ -1933,10 +1933,10 @@
         <v>71</v>
       </c>
       <c r="C51" s="30">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="D51" s="9">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="E51" s="9">
         <v>3000</v>
@@ -1949,13 +1949,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C52" s="30">
-        <v>46279</v>
+        <v>46293</v>
       </c>
       <c r="D52" s="9">
-        <v>1019</v>
+        <v>1044</v>
       </c>
       <c r="E52" s="9">
         <v>3000</v>
@@ -1968,7 +1968,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C53" s="30">
         <v>46293</v>
@@ -1987,7 +1987,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C54" s="30">
         <v>46281</v>
@@ -2179,8 +2179,8 @@
       <c r="A64" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B37:G45">
-    <sortCondition descending="1" ref="D37:D45"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B8:G13">
+    <sortCondition descending="1" ref="D8:D13"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804AE2DA-3A30-E543-952F-A5ABFED871DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360660D3-31B3-0745-919C-29F8EA6E7B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1514,13 +1514,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="C30" s="30">
-        <v>46287</v>
+        <v>46303</v>
       </c>
       <c r="D30" s="9">
-        <v>23927</v>
+        <v>23956</v>
       </c>
       <c r="E30" s="9">
         <v>27000</v>
@@ -1535,17 +1535,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C31" s="30">
-        <v>46141</v>
+        <v>46287</v>
       </c>
       <c r="D31" s="9">
-        <v>23812</v>
+        <v>23927</v>
       </c>
       <c r="E31" s="9">
         <v>27000</v>
       </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="11"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
     </row>
@@ -1554,19 +1556,17 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="C32" s="30">
-        <v>46261</v>
+        <v>46141</v>
       </c>
       <c r="D32" s="9">
-        <v>20932</v>
+        <v>23812</v>
       </c>
       <c r="E32" s="9">
-        <v>24000</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="11"/>
+        <v>27000</v>
+      </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
@@ -2179,8 +2179,8 @@
       <c r="A64" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B8:G13">
-    <sortCondition descending="1" ref="D8:D13"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B27:G32">
+    <sortCondition descending="1" ref="D27:D32"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360660D3-31B3-0745-919C-29F8EA6E7B76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FAFC9DC-E542-824B-B0A4-B7F886389EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1269,13 +1269,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C18" s="30">
-        <v>46258</v>
+        <v>46248</v>
       </c>
       <c r="D18" s="9">
-        <v>29848</v>
+        <v>29995</v>
       </c>
       <c r="E18" s="9">
         <v>33000</v>
@@ -1290,36 +1290,36 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C19" s="30">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="D19" s="9">
-        <v>27114</v>
+        <v>29848</v>
       </c>
       <c r="E19" s="9">
-        <v>30000</v>
-      </c>
+        <v>33000</v>
+      </c>
+      <c r="F19" s="7"/>
+      <c r="G19" s="11"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C20" s="30">
-        <v>46286</v>
+        <v>46265</v>
       </c>
       <c r="D20" s="9">
-        <v>27088</v>
+        <v>27114</v>
       </c>
       <c r="E20" s="9">
         <v>30000</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="11"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
     </row>
@@ -1328,18 +1328,18 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="C21" s="30">
-        <v>46254</v>
+        <v>46286</v>
       </c>
       <c r="D21" s="9">
-        <v>26978</v>
+        <v>27088</v>
       </c>
       <c r="E21" s="9">
         <v>30000</v>
       </c>
-      <c r="F21" s="7"/>
+      <c r="F21" s="3"/>
       <c r="G21" s="11"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
@@ -1349,13 +1349,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C22" s="30">
-        <v>46248</v>
+        <v>46254</v>
       </c>
       <c r="D22" s="9">
-        <v>26948</v>
+        <v>26978</v>
       </c>
       <c r="E22" s="9">
         <v>30000</v>
@@ -1370,13 +1370,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="C23" s="30">
-        <v>46204</v>
+        <v>46248</v>
       </c>
       <c r="D23" s="9">
-        <v>26924</v>
+        <v>26948</v>
       </c>
       <c r="E23" s="9">
         <v>30000</v>
@@ -1391,13 +1391,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C24" s="30">
-        <v>46248</v>
+        <v>46204</v>
       </c>
       <c r="D24" s="9">
-        <v>26817</v>
+        <v>26924</v>
       </c>
       <c r="E24" s="9">
         <v>30000</v>
@@ -2179,8 +2179,8 @@
       <c r="A64" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B27:G32">
-    <sortCondition descending="1" ref="D27:D32"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B16:G24">
+    <sortCondition descending="1" ref="D16:D24"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FAFC9DC-E542-824B-B0A4-B7F886389EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C928DD57-E03A-2943-AB02-A5F8788F3CDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t>No.</t>
   </si>
@@ -58,9 +58,6 @@
     <t>Still in Fleet</t>
   </si>
   <si>
-    <t>LV14MHGP</t>
-  </si>
-  <si>
     <t>LV14KRGP</t>
   </si>
   <si>
@@ -79,39 +76,21 @@
     <t>LV14GZGP</t>
   </si>
   <si>
-    <t>LV14DLGP</t>
-  </si>
-  <si>
     <t>LV14GBGP</t>
   </si>
   <si>
-    <t>LL74SSGP</t>
-  </si>
-  <si>
     <t>LL74SXGP</t>
   </si>
   <si>
     <t>LP28RXGP</t>
   </si>
   <si>
-    <t>KL21XDGP</t>
-  </si>
-  <si>
-    <t>KP13RNGP</t>
-  </si>
-  <si>
     <t>KP13YTGP</t>
   </si>
   <si>
     <t>KP13SMGP</t>
   </si>
   <si>
-    <t>KP13ZFGP</t>
-  </si>
-  <si>
-    <t>KP13TBGP</t>
-  </si>
-  <si>
     <t>KP13SBGP</t>
   </si>
   <si>
@@ -121,9 +100,6 @@
     <t>KR93JMGP</t>
   </si>
   <si>
-    <t>KS28KZGP</t>
-  </si>
-  <si>
     <t>KS49PKGP</t>
   </si>
   <si>
@@ -190,9 +166,6 @@
     <t>Recommended for Retirement</t>
   </si>
   <si>
-    <t>R</t>
-  </si>
-  <si>
     <t>MR01HNGP</t>
   </si>
   <si>
@@ -211,21 +184,12 @@
     <t>MR01KJGP</t>
   </si>
   <si>
-    <t>MR01KGGP</t>
-  </si>
-  <si>
     <t>MR01KRGP</t>
   </si>
   <si>
     <t>MR01HXGP</t>
   </si>
   <si>
-    <t>Accident Write-Off</t>
-  </si>
-  <si>
-    <t>Needs Eng. Hanger rubber bush (11102-M9Q-3000)  X2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Steering Stem was never replaced during accident repair. </t>
   </si>
   <si>
@@ -235,9 +199,6 @@
     <t>MR01JHGP</t>
   </si>
   <si>
-    <t>Accident repairs with a substandard touch</t>
-  </si>
-  <si>
     <t>ND17SHGP</t>
   </si>
   <si>
@@ -271,10 +232,13 @@
     <t>Date Serviced</t>
   </si>
   <si>
-    <t>Needs Swing lock Vush (50353-M9Q-0000) x2 and Engine mountings x2, Link Stopper rubber (50352-ADB-0000)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Steering Stem was never replaced during accident repair, needs Eng hanger (50351-ARA-0103) </t>
+  </si>
+  <si>
+    <t>Needs Swing lock Bush (50353-M9Q-0000) x2 and Engine mountings x2, Link Stopper rubber (50352-ADB-0000)</t>
+  </si>
+  <si>
+    <t>The accident repair is a mess and nowhere near an acceptable standard.</t>
   </si>
 </sst>
 </file>
@@ -286,7 +250,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -349,13 +313,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="20"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
@@ -363,7 +320,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -394,14 +351,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -444,12 +395,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -482,13 +444,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -522,7 +477,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -537,11 +492,11 @@
     <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -878,16 +833,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD8F41E-515C-324C-BF16-60C17361A01E}">
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="27" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21" style="32" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21" style="28" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="48.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="91.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="51" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="10.83203125" hidden="1"/>
@@ -900,8 +855,8 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="27" t="s">
-        <v>77</v>
+      <c r="C1" s="24" t="s">
+        <v>64</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>2</v>
@@ -914,16 +869,16 @@
       <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="19"/>
+      <c r="I1" s="16"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="28">
+        <v>24</v>
+      </c>
+      <c r="C2" s="25">
         <v>46293</v>
       </c>
       <c r="D2" s="10">
@@ -935,16 +890,16 @@
       <c r="F2" s="3"/>
       <c r="G2" s="11"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="19"/>
+      <c r="I2" s="16"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="28">
+        <v>15</v>
+      </c>
+      <c r="C3" s="25">
         <v>46280</v>
       </c>
       <c r="D3" s="10">
@@ -955,8 +910,8 @@
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="11"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="16" t="s">
+      <c r="H3" s="12"/>
+      <c r="I3" s="13" t="s">
         <v>6</v>
       </c>
     </row>
@@ -965,9 +920,9 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="28">
+        <v>17</v>
+      </c>
+      <c r="C4" s="25">
         <v>46276</v>
       </c>
       <c r="D4" s="10">
@@ -978,11 +933,11 @@
       </c>
       <c r="F4" s="3"/>
       <c r="G4" t="s">
-        <v>78</v>
-      </c>
-      <c r="H4" s="17"/>
-      <c r="I4" s="18" t="s">
-        <v>64</v>
+        <v>66</v>
+      </c>
+      <c r="H4" s="14"/>
+      <c r="I4" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -990,9 +945,9 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="28">
+        <v>21</v>
+      </c>
+      <c r="C5" s="25">
         <v>46275</v>
       </c>
       <c r="D5" s="10">
@@ -1003,9 +958,9 @@
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="11"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21" t="s">
-        <v>50</v>
+      <c r="H5" s="17"/>
+      <c r="I5" s="18" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -1013,9 +968,9 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="28">
+        <v>22</v>
+      </c>
+      <c r="C6" s="25">
         <v>46213</v>
       </c>
       <c r="D6" s="10">
@@ -1026,11 +981,11 @@
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H6" s="22"/>
-      <c r="I6" s="16" t="s">
-        <v>9</v>
+        <v>67</v>
+      </c>
+      <c r="H6" s="19"/>
+      <c r="I6" s="13" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -1038,9 +993,9 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="28">
+        <v>13</v>
+      </c>
+      <c r="C7" s="25">
         <v>46260</v>
       </c>
       <c r="D7" s="10">
@@ -1052,16 +1007,16 @@
       <c r="F7" s="3"/>
       <c r="G7" s="11"/>
       <c r="H7" s="4"/>
-      <c r="I7" s="25"/>
+      <c r="I7" s="22"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="28">
+        <v>20</v>
+      </c>
+      <c r="C8" s="25">
         <v>46269</v>
       </c>
       <c r="D8" s="10">
@@ -1072,7 +1027,7 @@
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="11" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -1081,21 +1036,21 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="29">
+      <c r="B9" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="26">
         <v>46302</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="21">
         <v>39089</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="21">
         <v>42000</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="11" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -1104,16 +1059,16 @@
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="29">
+      <c r="B10" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="26">
         <v>46275</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="21">
         <v>38987</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="21">
         <v>42000</v>
       </c>
       <c r="F10" s="7"/>
@@ -1123,16 +1078,16 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="29">
+      <c r="B11" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="26">
         <v>46280</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="21">
         <v>35995</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="21">
         <v>39000</v>
       </c>
       <c r="F11" s="7"/>
@@ -1142,16 +1097,16 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="29">
+      <c r="B12" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="26">
         <v>46267</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="21">
         <v>35951</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="21">
         <v>39000</v>
       </c>
       <c r="F12" s="7"/>
@@ -1164,9 +1119,9 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="30">
+        <v>27</v>
+      </c>
+      <c r="C13" s="27">
         <v>46293</v>
       </c>
       <c r="D13" s="9">
@@ -1185,9 +1140,9 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="30">
+        <v>29</v>
+      </c>
+      <c r="C14" s="27">
         <v>46272</v>
       </c>
       <c r="D14" s="9">
@@ -1206,9 +1161,9 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="30">
+        <v>37</v>
+      </c>
+      <c r="C15" s="27">
         <v>46272</v>
       </c>
       <c r="D15" s="9">
@@ -1217,7 +1172,7 @@
       <c r="E15" s="9">
         <v>36000</v>
       </c>
-      <c r="F15" s="26"/>
+      <c r="F15" s="23"/>
       <c r="G15" s="11"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -1227,9 +1182,9 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="30">
+        <v>23</v>
+      </c>
+      <c r="C16" s="27">
         <v>46216</v>
       </c>
       <c r="D16" s="9">
@@ -1240,7 +1195,7 @@
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="11" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -1250,9 +1205,9 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="30">
+        <v>31</v>
+      </c>
+      <c r="C17" s="27">
         <v>46275</v>
       </c>
       <c r="D17" s="9">
@@ -1269,9 +1224,9 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="30">
+        <v>25</v>
+      </c>
+      <c r="C18" s="27">
         <v>46248</v>
       </c>
       <c r="D18" s="9">
@@ -1290,9 +1245,9 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="30">
+        <v>33</v>
+      </c>
+      <c r="C19" s="27">
         <v>46258</v>
       </c>
       <c r="D19" s="9">
@@ -1309,9 +1264,9 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="30">
+        <v>39</v>
+      </c>
+      <c r="C20" s="27">
         <v>46265</v>
       </c>
       <c r="D20" s="9">
@@ -1328,9 +1283,9 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="30">
+        <v>49</v>
+      </c>
+      <c r="C21" s="27">
         <v>46286</v>
       </c>
       <c r="D21" s="9">
@@ -1349,9 +1304,9 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="30">
+        <v>11</v>
+      </c>
+      <c r="C22" s="27">
         <v>46254</v>
       </c>
       <c r="D22" s="9">
@@ -1372,7 +1327,7 @@
       <c r="B23" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="27">
         <v>46248</v>
       </c>
       <c r="D23" s="9">
@@ -1391,9 +1346,9 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="30">
+        <v>41</v>
+      </c>
+      <c r="C24" s="27">
         <v>46204</v>
       </c>
       <c r="D24" s="9">
@@ -1412,9 +1367,9 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="30">
+        <v>9</v>
+      </c>
+      <c r="C25" s="27">
         <v>46273</v>
       </c>
       <c r="D25" s="9">
@@ -1433,9 +1388,9 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="30">
+        <v>26</v>
+      </c>
+      <c r="C26" s="27">
         <v>46274</v>
       </c>
       <c r="D26" s="9">
@@ -1452,9 +1407,9 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="30">
+        <v>10</v>
+      </c>
+      <c r="C27" s="27">
         <v>46295</v>
       </c>
       <c r="D27" s="9">
@@ -1472,9 +1427,9 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="30">
+        <v>36</v>
+      </c>
+      <c r="C28" s="27">
         <v>46276</v>
       </c>
       <c r="D28" s="9">
@@ -1493,9 +1448,9 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" s="30">
+        <v>43</v>
+      </c>
+      <c r="C29" s="27">
         <v>46276</v>
       </c>
       <c r="D29" s="9">
@@ -1514,19 +1469,18 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="30">
-        <v>46303</v>
+        <v>34</v>
+      </c>
+      <c r="C30" s="27">
+        <v>46308</v>
       </c>
       <c r="D30" s="9">
-        <v>23956</v>
+        <v>23980</v>
       </c>
       <c r="E30" s="9">
         <v>27000</v>
       </c>
       <c r="F30" s="3"/>
-      <c r="G30" s="11"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
     </row>
@@ -1535,13 +1489,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="30">
-        <v>46287</v>
+        <v>47</v>
+      </c>
+      <c r="C31" s="27">
+        <v>46303</v>
       </c>
       <c r="D31" s="9">
-        <v>23927</v>
+        <v>23956</v>
       </c>
       <c r="E31" s="9">
         <v>27000</v>
@@ -1556,35 +1510,36 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="30">
-        <v>46141</v>
+        <v>7</v>
+      </c>
+      <c r="C32" s="27">
+        <v>46287</v>
       </c>
       <c r="D32" s="9">
-        <v>23812</v>
+        <v>23927</v>
       </c>
       <c r="E32" s="9">
         <v>27000</v>
       </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="11"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C33" s="30">
-        <v>46252</v>
+        <v>14</v>
+      </c>
+      <c r="C33" s="27">
+        <v>46141</v>
       </c>
       <c r="D33" s="9">
-        <v>20854</v>
+        <v>23812</v>
       </c>
       <c r="E33" s="9">
-        <v>24000</v>
-      </c>
-      <c r="F33" s="3"/>
+        <v>27000</v>
+      </c>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
     </row>
@@ -1593,9 +1548,9 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" s="30">
+        <v>48</v>
+      </c>
+      <c r="C34" s="27">
         <v>46287</v>
       </c>
       <c r="D34" s="9">
@@ -1613,9 +1568,9 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" s="30">
+        <v>45</v>
+      </c>
+      <c r="C35" s="27">
         <v>46287</v>
       </c>
       <c r="D35" s="9">
@@ -1632,9 +1587,9 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" s="30">
+        <v>30</v>
+      </c>
+      <c r="C36" s="27">
         <v>46248</v>
       </c>
       <c r="D36" s="9">
@@ -1653,9 +1608,9 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C37" s="30">
+        <v>19</v>
+      </c>
+      <c r="C37" s="27">
         <v>46274</v>
       </c>
       <c r="D37" s="9">
@@ -1674,9 +1629,9 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" s="30">
+        <v>38</v>
+      </c>
+      <c r="C38" s="27">
         <v>46241</v>
       </c>
       <c r="D38" s="9">
@@ -1695,9 +1650,9 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C39" s="30">
+        <v>44</v>
+      </c>
+      <c r="C39" s="27">
         <v>46286</v>
       </c>
       <c r="D39" s="9">
@@ -1714,9 +1669,9 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" s="30">
+        <v>18</v>
+      </c>
+      <c r="C40" s="27">
         <v>46274</v>
       </c>
       <c r="D40" s="9">
@@ -1735,9 +1690,9 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C41" s="30">
+        <v>50</v>
+      </c>
+      <c r="C41" s="27">
         <v>46283</v>
       </c>
       <c r="D41" s="9">
@@ -1755,9 +1710,9 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C42" s="30">
+        <v>32</v>
+      </c>
+      <c r="C42" s="27">
         <v>46276</v>
       </c>
       <c r="D42" s="9">
@@ -1776,9 +1731,9 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C43" s="30">
+        <v>28</v>
+      </c>
+      <c r="C43" s="27">
         <v>46171</v>
       </c>
       <c r="D43" s="9">
@@ -1797,9 +1752,9 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C44" s="30">
+        <v>46</v>
+      </c>
+      <c r="C44" s="27">
         <v>46266</v>
       </c>
       <c r="D44" s="9">
@@ -1816,9 +1771,9 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C45" s="30">
+        <v>53</v>
+      </c>
+      <c r="C45" s="27">
         <v>46297</v>
       </c>
       <c r="D45" s="9">
@@ -1835,9 +1790,9 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C46" s="30">
+        <v>59</v>
+      </c>
+      <c r="C46" s="27">
         <v>46296</v>
       </c>
       <c r="D46" s="9">
@@ -1854,13 +1809,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C47" s="30">
-        <v>46302</v>
+        <v>56</v>
+      </c>
+      <c r="C47" s="27">
+        <v>46308</v>
       </c>
       <c r="D47" s="9">
-        <v>2794</v>
+        <v>2904</v>
       </c>
       <c r="E47" s="9">
         <v>6000</v>
@@ -1873,16 +1828,16 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C48" s="30">
-        <v>46280</v>
+        <v>62</v>
+      </c>
+      <c r="C48" s="27">
+        <v>46302</v>
       </c>
       <c r="D48" s="9">
-        <v>1100</v>
+        <v>2794</v>
       </c>
       <c r="E48" s="9">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
@@ -1892,13 +1847,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C49" s="30">
-        <v>46297</v>
+        <v>60</v>
+      </c>
+      <c r="C49" s="27">
+        <v>46280</v>
       </c>
       <c r="D49" s="9">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="E49" s="9">
         <v>3000</v>
@@ -1911,13 +1866,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C50" s="30">
-        <v>46282</v>
+        <v>55</v>
+      </c>
+      <c r="C50" s="27">
+        <v>46297</v>
       </c>
       <c r="D50" s="9">
-        <v>1059</v>
+        <v>1098</v>
       </c>
       <c r="E50" s="9">
         <v>3000</v>
@@ -1930,9 +1885,9 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C51" s="30">
+        <v>58</v>
+      </c>
+      <c r="C51" s="27">
         <v>46286</v>
       </c>
       <c r="D51" s="9">
@@ -1949,9 +1904,9 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C52" s="30">
+        <v>57</v>
+      </c>
+      <c r="C52" s="27">
         <v>46293</v>
       </c>
       <c r="D52" s="9">
@@ -1968,9 +1923,9 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C53" s="30">
+        <v>61</v>
+      </c>
+      <c r="C53" s="27">
         <v>46293</v>
       </c>
       <c r="D53" s="9">
@@ -1987,9 +1942,9 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C54" s="30">
+        <v>54</v>
+      </c>
+      <c r="C54" s="27">
         <v>46281</v>
       </c>
       <c r="D54" s="9">
@@ -2002,185 +1957,18 @@
       <c r="I54" s="4"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A55" s="2">
+      <c r="A55" s="29">
         <v>54</v>
       </c>
-      <c r="B55" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C55" s="31"/>
-      <c r="D55" s="14">
-        <v>60031</v>
-      </c>
-      <c r="E55" s="14">
-        <v>63000</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G55" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A56" s="2">
-        <v>55</v>
-      </c>
-      <c r="B56" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C56" s="31"/>
-      <c r="D56" s="14">
-        <v>56725</v>
-      </c>
-      <c r="E56" s="14">
-        <v>60000</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A57" s="2">
-        <v>56</v>
-      </c>
-      <c r="B57" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C57" s="31"/>
-      <c r="D57" s="14">
-        <v>53997</v>
-      </c>
-      <c r="E57" s="14">
-        <v>57000</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A58" s="2">
-        <v>57</v>
-      </c>
-      <c r="B58" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="31"/>
-      <c r="D58" s="14">
-        <v>51012</v>
-      </c>
-      <c r="E58" s="14">
-        <v>54000</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A59" s="2">
-        <v>58</v>
-      </c>
-      <c r="B59" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" s="31"/>
-      <c r="D59" s="14">
-        <v>51007</v>
-      </c>
-      <c r="E59" s="14">
-        <v>54000</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G59" s="11"/>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A60" s="2">
-        <v>59</v>
-      </c>
-      <c r="B60" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C60" s="31"/>
-      <c r="D60" s="14">
-        <v>51002</v>
-      </c>
-      <c r="E60" s="14">
-        <v>54000</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G60" s="11"/>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A61" s="2">
-        <v>60</v>
-      </c>
-      <c r="B61" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="31"/>
-      <c r="D61" s="14">
-        <v>50855</v>
-      </c>
-      <c r="E61" s="14">
-        <v>54000</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G61" s="11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A62" s="2">
-        <v>61</v>
-      </c>
-      <c r="B62" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C62" s="31"/>
-      <c r="D62" s="14">
-        <v>44849</v>
-      </c>
-      <c r="E62" s="14">
-        <v>48000</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G62" s="11"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A63" s="2">
-        <v>62</v>
-      </c>
-      <c r="B63" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C63" s="31"/>
-      <c r="D63" s="14">
-        <v>982</v>
-      </c>
-      <c r="E63" s="14">
-        <v>3000</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G63" s="12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="2"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+    </row>
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B16:G24">
-    <sortCondition descending="1" ref="D16:D24"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B43:G50">
+    <sortCondition descending="1" ref="D43:D50"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C928DD57-E03A-2943-AB02-A5F8788F3CDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE331158-483A-EA43-8EA7-3AF93F679634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -495,7 +495,7 @@
     <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1224,13 +1224,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="C18" s="27">
-        <v>46248</v>
+        <v>46309</v>
       </c>
       <c r="D18" s="9">
-        <v>29995</v>
+        <v>30054</v>
       </c>
       <c r="E18" s="9">
         <v>33000</v>
@@ -1245,13 +1245,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C19" s="27">
-        <v>46258</v>
+        <v>46248</v>
       </c>
       <c r="D19" s="9">
-        <v>29848</v>
+        <v>29995</v>
       </c>
       <c r="E19" s="9">
         <v>33000</v>
@@ -1264,16 +1264,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C20" s="27">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="D20" s="9">
-        <v>27114</v>
+        <v>29848</v>
       </c>
       <c r="E20" s="9">
-        <v>30000</v>
+        <v>33000</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
@@ -1283,13 +1283,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C21" s="27">
-        <v>46286</v>
+        <v>46265</v>
       </c>
       <c r="D21" s="9">
-        <v>27088</v>
+        <v>27114</v>
       </c>
       <c r="E21" s="9">
         <v>30000</v>
@@ -1809,13 +1809,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C47" s="27">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D47" s="9">
-        <v>2904</v>
+        <v>2941</v>
       </c>
       <c r="E47" s="9">
         <v>6000</v>
@@ -1828,13 +1828,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C48" s="27">
-        <v>46302</v>
+        <v>46308</v>
       </c>
       <c r="D48" s="9">
-        <v>2794</v>
+        <v>2904</v>
       </c>
       <c r="E48" s="9">
         <v>6000</v>
@@ -1847,16 +1847,16 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C49" s="27">
-        <v>46280</v>
+        <v>46302</v>
       </c>
       <c r="D49" s="9">
-        <v>1100</v>
+        <v>2794</v>
       </c>
       <c r="E49" s="9">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
@@ -1967,8 +1967,8 @@
       <c r="A56" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B43:G50">
-    <sortCondition descending="1" ref="D43:D50"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B18:E22">
+    <sortCondition descending="1" ref="D18:D22"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE331158-483A-EA43-8EA7-3AF93F679634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CEAD26-8855-144D-9BFA-C2DD1A2C8ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1098,18 +1098,18 @@
         <v>11</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C12" s="26">
-        <v>46267</v>
+        <v>46310</v>
       </c>
       <c r="D12" s="21">
-        <v>35951</v>
+        <v>35995</v>
       </c>
       <c r="E12" s="21">
         <v>39000</v>
       </c>
-      <c r="F12" s="7"/>
+      <c r="F12" s="3"/>
       <c r="G12" s="11"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -1118,19 +1118,19 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="27">
-        <v>46293</v>
-      </c>
-      <c r="D13" s="9">
-        <v>33240</v>
-      </c>
-      <c r="E13" s="9">
-        <v>36000</v>
-      </c>
-      <c r="F13" s="3"/>
+      <c r="B13" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="26">
+        <v>46267</v>
+      </c>
+      <c r="D13" s="21">
+        <v>35951</v>
+      </c>
+      <c r="E13" s="21">
+        <v>39000</v>
+      </c>
+      <c r="F13" s="7"/>
       <c r="G13" s="11"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -1140,13 +1140,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C14" s="27">
-        <v>46272</v>
+        <v>46293</v>
       </c>
       <c r="D14" s="9">
-        <v>33043</v>
+        <v>33240</v>
       </c>
       <c r="E14" s="9">
         <v>36000</v>
@@ -1161,18 +1161,18 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C15" s="27">
         <v>46272</v>
       </c>
       <c r="D15" s="9">
-        <v>33030</v>
+        <v>33043</v>
       </c>
       <c r="E15" s="9">
         <v>36000</v>
       </c>
-      <c r="F15" s="23"/>
+      <c r="F15" s="3"/>
       <c r="G15" s="11"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -1182,21 +1182,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C16" s="27">
-        <v>46216</v>
+        <v>46272</v>
       </c>
       <c r="D16" s="9">
-        <v>32962</v>
+        <v>33030</v>
       </c>
       <c r="E16" s="9">
         <v>36000</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="11" t="s">
-        <v>63</v>
-      </c>
+      <c r="F16" s="23"/>
+      <c r="G16" s="11"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
     </row>
@@ -1205,19 +1203,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C17" s="27">
-        <v>46275</v>
+        <v>46216</v>
       </c>
       <c r="D17" s="9">
-        <v>32937</v>
+        <v>32962</v>
       </c>
       <c r="E17" s="9">
         <v>36000</v>
       </c>
       <c r="F17" s="3"/>
-      <c r="G17" s="11"/>
+      <c r="G17" s="11" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
@@ -1967,8 +1967,8 @@
       <c r="A56" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B18:E22">
-    <sortCondition descending="1" ref="D18:D22"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B10:G17">
+    <sortCondition descending="1" ref="D10:D17"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CEAD26-8855-144D-9BFA-C2DD1A2C8ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0CEC79-B34C-BB47-A52B-F1A163C093CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -993,18 +993,18 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C7" s="25">
-        <v>46260</v>
+        <v>46310</v>
       </c>
       <c r="D7" s="10">
-        <v>41964</v>
+        <v>42063</v>
       </c>
       <c r="E7" s="10">
         <v>45000</v>
       </c>
-      <c r="F7" s="3"/>
+      <c r="F7" s="7"/>
       <c r="G7" s="11"/>
       <c r="H7" s="4"/>
       <c r="I7" s="22"/>
@@ -1014,21 +1014,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C8" s="25">
-        <v>46269</v>
+        <v>46260</v>
       </c>
       <c r="D8" s="10">
-        <v>41702</v>
+        <v>41964</v>
       </c>
       <c r="E8" s="10">
         <v>45000</v>
       </c>
       <c r="F8" s="3"/>
-      <c r="G8" s="11" t="s">
-        <v>51</v>
-      </c>
+      <c r="G8" s="11"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
     </row>
@@ -1036,21 +1034,21 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="26">
-        <v>46302</v>
-      </c>
-      <c r="D9" s="21">
-        <v>39089</v>
-      </c>
-      <c r="E9" s="21">
-        <v>42000</v>
+      <c r="B9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="25">
+        <v>46269</v>
+      </c>
+      <c r="D9" s="10">
+        <v>41702</v>
+      </c>
+      <c r="E9" s="10">
+        <v>45000</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="11" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -1060,19 +1058,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C10" s="26">
-        <v>46275</v>
+        <v>46302</v>
       </c>
       <c r="D10" s="21">
-        <v>38987</v>
+        <v>39089</v>
       </c>
       <c r="E10" s="21">
         <v>42000</v>
       </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="11"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="11" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
@@ -1245,13 +1245,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C19" s="27">
-        <v>46248</v>
+        <v>46310</v>
       </c>
       <c r="D19" s="9">
-        <v>29995</v>
+        <v>30016</v>
       </c>
       <c r="E19" s="9">
         <v>33000</v>
@@ -1264,17 +1264,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C20" s="27">
-        <v>46258</v>
+        <v>46248</v>
       </c>
       <c r="D20" s="9">
-        <v>29848</v>
+        <v>29995</v>
       </c>
       <c r="E20" s="9">
         <v>33000</v>
       </c>
+      <c r="F20" s="7"/>
+      <c r="G20" s="11"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
     </row>
@@ -1283,19 +1285,17 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C21" s="27">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="D21" s="9">
-        <v>27114</v>
+        <v>29848</v>
       </c>
       <c r="E21" s="9">
-        <v>30000</v>
-      </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="11"/>
+        <v>33000</v>
+      </c>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
     </row>
@@ -1304,13 +1304,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="C22" s="27">
-        <v>46254</v>
+        <v>46310</v>
       </c>
       <c r="D22" s="9">
-        <v>26978</v>
+        <v>27349</v>
       </c>
       <c r="E22" s="9">
         <v>30000</v>
@@ -1325,18 +1325,18 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="C23" s="27">
-        <v>46248</v>
+        <v>46265</v>
       </c>
       <c r="D23" s="9">
-        <v>26948</v>
+        <v>27114</v>
       </c>
       <c r="E23" s="9">
         <v>30000</v>
       </c>
-      <c r="F23" s="7"/>
+      <c r="F23" s="3"/>
       <c r="G23" s="11"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
@@ -1346,13 +1346,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C24" s="27">
-        <v>46204</v>
+        <v>46254</v>
       </c>
       <c r="D24" s="9">
-        <v>26924</v>
+        <v>26978</v>
       </c>
       <c r="E24" s="9">
         <v>30000</v>
@@ -1367,18 +1367,18 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="C25" s="27">
-        <v>46273</v>
+        <v>46204</v>
       </c>
       <c r="D25" s="9">
-        <v>26815</v>
+        <v>26924</v>
       </c>
       <c r="E25" s="9">
         <v>30000</v>
       </c>
-      <c r="F25" s="3"/>
+      <c r="F25" s="7"/>
       <c r="G25" s="11"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
@@ -1388,17 +1388,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C26" s="27">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="D26" s="9">
-        <v>26753</v>
+        <v>26815</v>
       </c>
       <c r="E26" s="9">
         <v>30000</v>
       </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="11"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
     </row>
@@ -1407,18 +1409,17 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C27" s="27">
-        <v>46295</v>
+        <v>46274</v>
       </c>
       <c r="D27" s="9">
-        <v>26668</v>
+        <v>26753</v>
       </c>
       <c r="E27" s="9">
         <v>30000</v>
       </c>
-      <c r="F27" s="3"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
     </row>
@@ -1427,19 +1428,18 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C28" s="27">
-        <v>46276</v>
+        <v>46295</v>
       </c>
       <c r="D28" s="9">
-        <v>24153</v>
+        <v>26668</v>
       </c>
       <c r="E28" s="9">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="F28" s="3"/>
-      <c r="G28" s="11"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
     </row>
@@ -1448,18 +1448,18 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C29" s="27">
         <v>46276</v>
       </c>
       <c r="D29" s="9">
-        <v>24046</v>
+        <v>24153</v>
       </c>
       <c r="E29" s="9">
         <v>27000</v>
       </c>
-      <c r="F29" s="7"/>
+      <c r="F29" s="3"/>
       <c r="G29" s="11"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
@@ -1731,19 +1731,17 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C43" s="27">
-        <v>46171</v>
+        <v>46310</v>
       </c>
       <c r="D43" s="9">
-        <v>8977</v>
+        <v>9131</v>
       </c>
       <c r="E43" s="9">
         <v>12000</v>
       </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="11"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
     </row>
@@ -1752,17 +1750,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C44" s="27">
-        <v>46266</v>
+        <v>46171</v>
       </c>
       <c r="D44" s="9">
-        <v>5970</v>
+        <v>8977</v>
       </c>
       <c r="E44" s="9">
-        <v>9000</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="11"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
     </row>
@@ -1967,8 +1967,8 @@
       <c r="A56" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B10:G17">
-    <sortCondition descending="1" ref="D10:D17"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:G55">
+    <sortCondition descending="1" ref="D2:D55"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0CEC79-B34C-BB47-A52B-F1A163C093CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6437D72D-9946-934E-BA61-996D78EB8262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -993,18 +993,18 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="C7" s="25">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="D7" s="10">
-        <v>42063</v>
+        <v>44892</v>
       </c>
       <c r="E7" s="10">
-        <v>45000</v>
-      </c>
-      <c r="F7" s="7"/>
+        <v>48000</v>
+      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="11"/>
       <c r="H7" s="4"/>
       <c r="I7" s="22"/>
@@ -1014,18 +1014,18 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C8" s="25">
-        <v>46260</v>
+        <v>46310</v>
       </c>
       <c r="D8" s="10">
-        <v>41964</v>
+        <v>42063</v>
       </c>
       <c r="E8" s="10">
         <v>45000</v>
       </c>
-      <c r="F8" s="3"/>
+      <c r="F8" s="7"/>
       <c r="G8" s="11"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -1866,16 +1866,16 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C50" s="27">
-        <v>46297</v>
+        <v>46314</v>
       </c>
       <c r="D50" s="9">
-        <v>1098</v>
+        <v>2780</v>
       </c>
       <c r="E50" s="9">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
@@ -1885,13 +1885,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C51" s="27">
-        <v>46286</v>
+        <v>46297</v>
       </c>
       <c r="D51" s="9">
-        <v>1045</v>
+        <v>1098</v>
       </c>
       <c r="E51" s="9">
         <v>3000</v>
@@ -1904,13 +1904,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C52" s="27">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="D52" s="9">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="E52" s="9">
         <v>3000</v>
@@ -1923,13 +1923,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C53" s="27">
         <v>46293</v>
       </c>
       <c r="D53" s="9">
-        <v>1011</v>
+        <v>1044</v>
       </c>
       <c r="E53" s="9">
         <v>3000</v>
@@ -1942,13 +1942,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C54" s="27">
-        <v>46281</v>
+        <v>46293</v>
       </c>
       <c r="D54" s="9">
-        <v>889</v>
+        <v>1011</v>
       </c>
       <c r="E54" s="9">
         <v>3000</v>
@@ -1967,8 +1967,8 @@
       <c r="A56" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:G55">
-    <sortCondition descending="1" ref="D2:D55"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B46:E54">
+    <sortCondition descending="1" ref="D46:D54"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6437D72D-9946-934E-BA61-996D78EB8262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26810327-72F3-B347-8083-8D2181B76D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1079,18 +1079,18 @@
         <v>10</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C11" s="26">
-        <v>46280</v>
+        <v>46317</v>
       </c>
       <c r="D11" s="21">
-        <v>35995</v>
+        <v>36021</v>
       </c>
       <c r="E11" s="21">
         <v>39000</v>
       </c>
-      <c r="F11" s="7"/>
+      <c r="F11" s="3"/>
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -1098,10 +1098,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C12" s="26">
-        <v>46310</v>
+        <v>46280</v>
       </c>
       <c r="D12" s="21">
         <v>35995</v>
@@ -1109,7 +1109,7 @@
       <c r="E12" s="21">
         <v>39000</v>
       </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="7"/>
       <c r="G12" s="11"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -1119,18 +1119,18 @@
         <v>12</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C13" s="26">
-        <v>46267</v>
+        <v>46310</v>
       </c>
       <c r="D13" s="21">
-        <v>35951</v>
+        <v>35995</v>
       </c>
       <c r="E13" s="21">
         <v>39000</v>
       </c>
-      <c r="F13" s="7"/>
+      <c r="F13" s="3"/>
       <c r="G13" s="11"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -1139,19 +1139,19 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="27">
-        <v>46293</v>
-      </c>
-      <c r="D14" s="9">
-        <v>33240</v>
-      </c>
-      <c r="E14" s="9">
-        <v>36000</v>
-      </c>
-      <c r="F14" s="3"/>
+      <c r="B14" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="26">
+        <v>46267</v>
+      </c>
+      <c r="D14" s="21">
+        <v>35951</v>
+      </c>
+      <c r="E14" s="21">
+        <v>39000</v>
+      </c>
+      <c r="F14" s="7"/>
       <c r="G14" s="11"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
@@ -1161,13 +1161,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C15" s="27">
-        <v>46272</v>
+        <v>46293</v>
       </c>
       <c r="D15" s="9">
-        <v>33043</v>
+        <v>33240</v>
       </c>
       <c r="E15" s="9">
         <v>36000</v>
@@ -1967,8 +1967,8 @@
       <c r="A56" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B46:E54">
-    <sortCondition descending="1" ref="D46:D54"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B10:G15">
+    <sortCondition descending="1" ref="D10:D15"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26810327-72F3-B347-8083-8D2181B76D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B00B2F-F4CF-C040-B5BB-B374E4BC54DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1014,19 +1014,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C8" s="25">
-        <v>46310</v>
+        <v>46317</v>
       </c>
       <c r="D8" s="10">
-        <v>42063</v>
+        <v>44886</v>
       </c>
       <c r="E8" s="10">
-        <v>45000</v>
-      </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="11"/>
+        <v>48000</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
     </row>
@@ -1035,21 +1037,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C9" s="25">
-        <v>46269</v>
+        <v>46310</v>
       </c>
       <c r="D9" s="10">
-        <v>41702</v>
+        <v>42063</v>
       </c>
       <c r="E9" s="10">
         <v>45000</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="11" t="s">
-        <v>51</v>
-      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="11"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
     </row>
@@ -1967,8 +1967,8 @@
       <c r="A56" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B10:G15">
-    <sortCondition descending="1" ref="D10:D15"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:G9">
+    <sortCondition descending="1" ref="D2:D9"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B00B2F-F4CF-C040-B5BB-B374E4BC54DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979BDEA6-089B-9747-BCF9-FE9B0ECD0A2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1079,18 +1079,18 @@
         <v>10</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C11" s="26">
-        <v>46317</v>
+        <v>46321</v>
       </c>
       <c r="D11" s="21">
-        <v>36021</v>
+        <v>38758</v>
       </c>
       <c r="E11" s="21">
-        <v>39000</v>
-      </c>
-      <c r="F11" s="3"/>
+        <v>42000</v>
+      </c>
+      <c r="F11" s="7"/>
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -1098,18 +1098,18 @@
         <v>11</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C12" s="26">
-        <v>46280</v>
+        <v>46317</v>
       </c>
       <c r="D12" s="21">
-        <v>35995</v>
+        <v>36021</v>
       </c>
       <c r="E12" s="21">
         <v>39000</v>
       </c>
-      <c r="F12" s="7"/>
+      <c r="F12" s="3"/>
       <c r="G12" s="11"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -1224,18 +1224,18 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C18" s="27">
-        <v>46309</v>
+        <v>46321</v>
       </c>
       <c r="D18" s="9">
-        <v>30054</v>
+        <v>30127</v>
       </c>
       <c r="E18" s="9">
         <v>33000</v>
       </c>
-      <c r="F18" s="7"/>
+      <c r="F18" s="3"/>
       <c r="G18" s="11"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
@@ -1245,13 +1245,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="C19" s="27">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="D19" s="9">
-        <v>30016</v>
+        <v>30054</v>
       </c>
       <c r="E19" s="9">
         <v>33000</v>
@@ -1264,13 +1264,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C20" s="27">
-        <v>46248</v>
+        <v>46310</v>
       </c>
       <c r="D20" s="9">
-        <v>29995</v>
+        <v>30016</v>
       </c>
       <c r="E20" s="9">
         <v>33000</v>
@@ -1285,17 +1285,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C21" s="27">
-        <v>46258</v>
+        <v>46248</v>
       </c>
       <c r="D21" s="9">
-        <v>29848</v>
+        <v>29995</v>
       </c>
       <c r="E21" s="9">
         <v>33000</v>
       </c>
+      <c r="F21" s="7"/>
+      <c r="G21" s="11"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
     </row>
@@ -1304,19 +1306,17 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C22" s="27">
-        <v>46310</v>
+        <v>46258</v>
       </c>
       <c r="D22" s="9">
-        <v>27349</v>
+        <v>29848</v>
       </c>
       <c r="E22" s="9">
-        <v>30000</v>
-      </c>
-      <c r="F22" s="7"/>
-      <c r="G22" s="11"/>
+        <v>33000</v>
+      </c>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
     </row>
@@ -1325,18 +1325,18 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C23" s="27">
-        <v>46265</v>
+        <v>46310</v>
       </c>
       <c r="D23" s="9">
-        <v>27114</v>
+        <v>27349</v>
       </c>
       <c r="E23" s="9">
         <v>30000</v>
       </c>
-      <c r="F23" s="3"/>
+      <c r="F23" s="7"/>
       <c r="G23" s="11"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
@@ -1650,17 +1650,18 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C39" s="27">
-        <v>46286</v>
+        <v>46321</v>
       </c>
       <c r="D39" s="9">
-        <v>14912</v>
+        <v>14926</v>
       </c>
       <c r="E39" s="9">
         <v>18000</v>
       </c>
+      <c r="F39" s="3"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
     </row>
@@ -1669,19 +1670,17 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C40" s="27">
-        <v>46274</v>
+        <v>46286</v>
       </c>
       <c r="D40" s="9">
-        <v>14692</v>
+        <v>14912</v>
       </c>
       <c r="E40" s="9">
         <v>18000</v>
       </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="11"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
     </row>
@@ -1690,18 +1689,19 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="C41" s="27">
-        <v>46283</v>
+        <v>46274</v>
       </c>
       <c r="D41" s="9">
-        <v>11920</v>
+        <v>14692</v>
       </c>
       <c r="E41" s="9">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="F41" s="3"/>
+      <c r="G41" s="11"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
     </row>
@@ -1967,8 +1967,8 @@
       <c r="A56" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:G9">
-    <sortCondition descending="1" ref="D2:D9"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:G54">
+    <sortCondition descending="1" ref="D2:D54"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979BDEA6-089B-9747-BCF9-FE9B0ECD0A2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0FAD0F2-AEF9-B64F-A29C-0BEEA202AD53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -1160,17 +1160,17 @@
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="27">
-        <v>46293</v>
-      </c>
-      <c r="D15" s="9">
-        <v>33240</v>
-      </c>
-      <c r="E15" s="9">
-        <v>36000</v>
+      <c r="C15" s="26">
+        <v>46321</v>
+      </c>
+      <c r="D15" s="21">
+        <v>35814</v>
+      </c>
+      <c r="E15" s="21">
+        <v>39000</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="11"/>
@@ -1967,8 +1967,8 @@
       <c r="A56" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:G54">
-    <sortCondition descending="1" ref="D2:D54"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B9:G15">
+    <sortCondition descending="1" ref="D9:D15"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0FAD0F2-AEF9-B64F-A29C-0BEEA202AD53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A310623-4CC9-BD47-9CC0-4E56A4F21432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -897,19 +897,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C3" s="25">
-        <v>46280</v>
+        <v>46322</v>
       </c>
       <c r="D3" s="10">
-        <v>47926</v>
+        <v>48045</v>
       </c>
       <c r="E3" s="10">
         <v>51000</v>
       </c>
       <c r="F3" s="3"/>
-      <c r="G3" s="11"/>
+      <c r="G3" s="11" t="s">
+        <v>67</v>
+      </c>
       <c r="H3" s="12"/>
       <c r="I3" s="13" t="s">
         <v>6</v>
@@ -920,21 +922,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="25">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="D4" s="10">
-        <v>45073</v>
+        <v>47926</v>
       </c>
       <c r="E4" s="10">
-        <v>48000</v>
+        <v>51000</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" t="s">
-        <v>66</v>
-      </c>
+      <c r="G4" s="11"/>
       <c r="H4" s="14"/>
       <c r="I4" s="15" t="s">
         <v>52</v>
@@ -945,19 +945,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C5" s="25">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D5" s="10">
-        <v>45003</v>
+        <v>45073</v>
       </c>
       <c r="E5" s="10">
         <v>48000</v>
       </c>
       <c r="F5" s="3"/>
-      <c r="G5" s="11"/>
+      <c r="G5" t="s">
+        <v>66</v>
+      </c>
       <c r="H5" s="17"/>
       <c r="I5" s="18" t="s">
         <v>42</v>
@@ -968,21 +970,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="25">
-        <v>46213</v>
+        <v>46275</v>
       </c>
       <c r="D6" s="10">
-        <v>44912</v>
+        <v>45003</v>
       </c>
       <c r="E6" s="10">
         <v>48000</v>
       </c>
       <c r="F6" s="3"/>
-      <c r="G6" s="11" t="s">
-        <v>67</v>
-      </c>
+      <c r="G6" s="11"/>
       <c r="H6" s="19"/>
       <c r="I6" s="13" t="s">
         <v>8</v>
@@ -1967,8 +1967,8 @@
       <c r="A56" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B9:G15">
-    <sortCondition descending="1" ref="D9:D15"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:G6">
+    <sortCondition descending="1" ref="D2:D6"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fleet Mileage.xlsx
+++ b/Fleet Mileage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/Business/scootdr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A310623-4CC9-BD47-9CC0-4E56A4F21432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959845BF-89ED-D34D-93A2-0B8C6865C03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25540" windowHeight="15500" xr2:uid="{DD62F603-65F5-B64B-908C-44E0CEED2B19}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>No.</t>
   </si>
@@ -239,6 +239,12 @@
   </si>
   <si>
     <t>The accident repair is a mess and nowhere near an acceptable standard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was in accident repair and Needed New Chassis </t>
+  </si>
+  <si>
+    <t>NF98CLGP</t>
   </si>
 </sst>
 </file>
@@ -1098,18 +1104,18 @@
         <v>11</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C12" s="26">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="D12" s="21">
-        <v>36021</v>
+        <v>36125</v>
       </c>
       <c r="E12" s="21">
         <v>39000</v>
       </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="23"/>
       <c r="G12" s="11"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -1119,13 +1125,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" s="26">
-        <v>46310</v>
+        <v>46317</v>
       </c>
       <c r="D13" s="21">
-        <v>35995</v>
+        <v>36021</v>
       </c>
       <c r="E13" s="21">
         <v>39000</v>
@@ -1140,18 +1146,18 @@
         <v>13</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C14" s="26">
-        <v>46267</v>
+        <v>46310</v>
       </c>
       <c r="D14" s="21">
-        <v>35951</v>
+        <v>35995</v>
       </c>
       <c r="E14" s="21">
         <v>39000</v>
       </c>
-      <c r="F14" s="7"/>
+      <c r="F14" s="3"/>
       <c r="G14" s="11"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
@@ -1161,18 +1167,18 @@
         <v>14</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C15" s="26">
-        <v>46321</v>
+        <v>46267</v>
       </c>
       <c r="D15" s="21">
-        <v>35814</v>
+        <v>35951</v>
       </c>
       <c r="E15" s="21">
         <v>39000</v>
       </c>
-      <c r="F15" s="3"/>
+      <c r="F15" s="7"/>
       <c r="G15" s="11"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -1181,19 +1187,19 @@
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="27">
-        <v>46272</v>
-      </c>
-      <c r="D16" s="9">
-        <v>33030</v>
-      </c>
-      <c r="E16" s="9">
-        <v>36000</v>
-      </c>
-      <c r="F16" s="23"/>
+      <c r="B16" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="26">
+        <v>46321</v>
+      </c>
+      <c r="D16" s="21">
+        <v>35814</v>
+      </c>
+      <c r="E16" s="21">
+        <v>39000</v>
+      </c>
+      <c r="F16" s="3"/>
       <c r="G16" s="11"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -1540,6 +1546,9 @@
       <c r="E33" s="9">
         <v>27000</v>
       </c>
+      <c r="G33" t="s">
+        <v>68</v>
+      </c>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
     </row>
@@ -1548,18 +1557,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C34" s="27">
-        <v>46287</v>
+        <v>46324</v>
       </c>
       <c r="D34" s="9">
-        <v>20820</v>
+        <v>20953</v>
       </c>
       <c r="E34" s="9">
         <v>24000</v>
       </c>
-      <c r="F34" s="3"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="11"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
     </row>
@@ -1568,17 +1578,18 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C35" s="27">
         <v>46287</v>
       </c>
       <c r="D35" s="9">
-        <v>18344</v>
+        <v>20820</v>
       </c>
       <c r="E35" s="9">
-        <v>21000</v>
-      </c>
+        <v>24000</v>
+      </c>
+      <c r="F35" s="3"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
     </row>
@@ -1587,19 +1598,17 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C36" s="27">
-        <v>46248</v>
+        <v>46287</v>
       </c>
       <c r="D36" s="9">
-        <v>17993</v>
+        <v>18344</v>
       </c>
       <c r="E36" s="9">
         <v>21000</v>
       </c>
-      <c r="F36" s="7"/>
-      <c r="G36" s="11"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
     </row>
@@ -1960,6 +1969,18 @@
       <c r="A55" s="29">
         <v>54</v>
       </c>
+      <c r="B55" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C55" s="27">
+        <v>46321</v>
+      </c>
+      <c r="D55" s="9">
+        <v>1</v>
+      </c>
+      <c r="E55" s="9">
+        <v>1000</v>
+      </c>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
     </row>
@@ -1967,8 +1988,8 @@
       <c r="A56" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:G6">
-    <sortCondition descending="1" ref="D2:D6"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:G54">
+    <sortCondition descending="1" ref="D2:D54"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
